--- a/research/traditional_assets/database/data/oman/oman_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_construction_supplies.xlsx
@@ -1534,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1671,22 +1671,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.100696673382856</v>
+        <v>0.1005838783727817</v>
       </c>
       <c r="C2">
-        <v>326.834849772522</v>
+        <v>323.8969743282767</v>
       </c>
       <c r="D2">
-        <v>261.734849772522</v>
+        <v>262.0631743282767</v>
       </c>
       <c r="E2">
-        <v>-1.72</v>
+        <v>1.5462</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.2662</v>
       </c>
       <c r="G2">
         <v>65.09999999999999</v>
@@ -1707,28 +1707,28 @@
         <v>33.296</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.16428986</v>
       </c>
       <c r="N2">
-        <v>33.296</v>
+        <v>33.13171014</v>
       </c>
       <c r="O2">
-        <v>4.9944</v>
+        <v>4.969756521</v>
       </c>
       <c r="P2">
-        <v>28.3016</v>
+        <v>28.161953619</v>
       </c>
       <c r="Q2">
-        <v>28.9056</v>
+        <v>28.765953619</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.100696673382856</v>
+        <v>0.1011680084573552</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7216307604550376</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>202.6661901105766</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1753,22 +1753,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1005838783727817</v>
+        <v>0.1004710833627074</v>
       </c>
       <c r="C3">
-        <v>323.8969743282767</v>
+        <v>320.9599236301911</v>
       </c>
       <c r="D3">
-        <v>262.0631743282767</v>
+        <v>262.3923236301911</v>
       </c>
       <c r="E3">
-        <v>1.5462</v>
+        <v>4.8124</v>
       </c>
       <c r="F3">
-        <v>3.2662</v>
+        <v>6.5324</v>
       </c>
       <c r="G3">
         <v>65.09999999999999</v>
@@ -1789,28 +1789,28 @@
         <v>33.296</v>
       </c>
       <c r="M3">
-        <v>0.16428986</v>
+        <v>0.32857972</v>
       </c>
       <c r="N3">
-        <v>33.13171014</v>
+        <v>32.96742028</v>
       </c>
       <c r="O3">
-        <v>4.969756521</v>
+        <v>4.945113042</v>
       </c>
       <c r="P3">
-        <v>28.161953619</v>
+        <v>28.022307238</v>
       </c>
       <c r="Q3">
-        <v>28.765953619</v>
+        <v>28.626307238</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1011680084573552</v>
+        <v>0.1016489626150076</v>
       </c>
       <c r="T3">
-        <v>0.7216307604550376</v>
+        <v>0.7278992054325732</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>202.6661901105766</v>
+        <v>101.3330950552883</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1835,22 +1835,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1004710833627074</v>
+        <v>0.1003582883526331</v>
       </c>
       <c r="C4">
-        <v>320.9599236301911</v>
+        <v>318.0237007897977</v>
       </c>
       <c r="D4">
-        <v>262.3923236301911</v>
+        <v>262.7223007897978</v>
       </c>
       <c r="E4">
-        <v>4.8124</v>
+        <v>8.0786</v>
       </c>
       <c r="F4">
-        <v>6.5324</v>
+        <v>9.7986</v>
       </c>
       <c r="G4">
         <v>65.09999999999999</v>
@@ -1871,28 +1871,28 @@
         <v>33.296</v>
       </c>
       <c r="M4">
-        <v>0.32857972</v>
+        <v>0.49286958</v>
       </c>
       <c r="N4">
-        <v>32.96742028</v>
+        <v>32.80313042</v>
       </c>
       <c r="O4">
-        <v>4.945113042</v>
+        <v>4.920469563</v>
       </c>
       <c r="P4">
-        <v>28.022307238</v>
+        <v>27.882660857</v>
       </c>
       <c r="Q4">
-        <v>28.626307238</v>
+        <v>28.486660857</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1016489626150076</v>
+        <v>0.10213983335323</v>
       </c>
       <c r="T4">
-        <v>0.7278992054325732</v>
+        <v>0.7342968966983052</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>101.3330950552883</v>
+        <v>67.55539670352552</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1917,22 +1917,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1003582883526331</v>
+        <v>0.1002454933425588</v>
       </c>
       <c r="C5">
-        <v>318.0237007897977</v>
+        <v>315.0883089343002</v>
       </c>
       <c r="D5">
-        <v>262.7223007897978</v>
+        <v>263.0531089343003</v>
       </c>
       <c r="E5">
-        <v>8.0786</v>
+        <v>11.3448</v>
       </c>
       <c r="F5">
-        <v>9.7986</v>
+        <v>13.0648</v>
       </c>
       <c r="G5">
         <v>65.09999999999999</v>
@@ -1953,28 +1953,28 @@
         <v>33.296</v>
       </c>
       <c r="M5">
-        <v>0.49286958</v>
+        <v>0.6571594399999999</v>
       </c>
       <c r="N5">
-        <v>32.80313042</v>
+        <v>32.63884056</v>
       </c>
       <c r="O5">
-        <v>4.920469563</v>
+        <v>4.895826083999999</v>
       </c>
       <c r="P5">
-        <v>27.882660857</v>
+        <v>27.743014476</v>
       </c>
       <c r="Q5">
-        <v>28.486660857</v>
+        <v>28.347014476</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.10213983335323</v>
+        <v>0.1026409305651655</v>
       </c>
       <c r="T5">
-        <v>0.7342968966983052</v>
+        <v>0.7408278731987402</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>67.55539670352552</v>
+        <v>50.66654752764413</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1999,22 +1999,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1002454933425588</v>
+        <v>0.1001326983324845</v>
       </c>
       <c r="C6">
-        <v>315.0883089343002</v>
+        <v>312.1537512066731</v>
       </c>
       <c r="D6">
-        <v>263.0531089343003</v>
+        <v>263.3847512066731</v>
       </c>
       <c r="E6">
-        <v>11.3448</v>
+        <v>14.611</v>
       </c>
       <c r="F6">
-        <v>13.0648</v>
+        <v>16.331</v>
       </c>
       <c r="G6">
         <v>65.09999999999999</v>
@@ -2035,28 +2035,28 @@
         <v>33.296</v>
       </c>
       <c r="M6">
-        <v>0.6571594399999999</v>
+        <v>0.8214492999999999</v>
       </c>
       <c r="N6">
-        <v>32.63884056</v>
+        <v>32.4745507</v>
       </c>
       <c r="O6">
-        <v>4.895826083999999</v>
+        <v>4.871182605</v>
       </c>
       <c r="P6">
-        <v>27.743014476</v>
+        <v>27.603368095</v>
       </c>
       <c r="Q6">
-        <v>28.347014476</v>
+        <v>28.207368095</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1026409305651655</v>
+        <v>0.103152577192089</v>
       </c>
       <c r="T6">
-        <v>0.7408278731987402</v>
+        <v>0.7474963439412895</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.66654752764413</v>
+        <v>40.53323802211531</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1001326983324845</v>
+        <v>0.1000199033224103</v>
       </c>
       <c r="C7">
-        <v>312.1537512066731</v>
+        <v>309.2200307657604</v>
       </c>
       <c r="D7">
-        <v>263.3847512066731</v>
+        <v>263.7172307657605</v>
       </c>
       <c r="E7">
-        <v>14.611</v>
+        <v>17.8772</v>
       </c>
       <c r="F7">
-        <v>16.331</v>
+        <v>19.5972</v>
       </c>
       <c r="G7">
         <v>65.09999999999999</v>
@@ -2117,28 +2117,28 @@
         <v>33.296</v>
       </c>
       <c r="M7">
-        <v>0.8214492999999999</v>
+        <v>0.9857391599999999</v>
       </c>
       <c r="N7">
-        <v>32.4745507</v>
+        <v>32.31026084</v>
       </c>
       <c r="O7">
-        <v>4.871182605</v>
+        <v>4.846539126</v>
       </c>
       <c r="P7">
-        <v>27.603368095</v>
+        <v>27.463721714</v>
       </c>
       <c r="Q7">
-        <v>28.207368095</v>
+        <v>28.067721714</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.103152577192089</v>
+        <v>0.1036751099174577</v>
       </c>
       <c r="T7">
-        <v>0.7474963439412895</v>
+        <v>0.7543066970400631</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.53323802211531</v>
+        <v>33.77769835176275</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2163,22 +2163,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1000199033224103</v>
+        <v>0.09990710831233598</v>
       </c>
       <c r="C8">
-        <v>309.2200307657604</v>
+        <v>306.2871507863767</v>
       </c>
       <c r="D8">
-        <v>263.7172307657605</v>
+        <v>264.0505507863767</v>
       </c>
       <c r="E8">
-        <v>17.8772</v>
+        <v>21.1434</v>
       </c>
       <c r="F8">
-        <v>19.5972</v>
+        <v>22.8634</v>
       </c>
       <c r="G8">
         <v>65.09999999999999</v>
@@ -2199,28 +2199,28 @@
         <v>33.296</v>
       </c>
       <c r="M8">
-        <v>0.9857391599999999</v>
+        <v>1.15002902</v>
       </c>
       <c r="N8">
-        <v>32.31026084</v>
+        <v>32.14597098</v>
       </c>
       <c r="O8">
-        <v>4.846539126</v>
+        <v>4.821895647</v>
       </c>
       <c r="P8">
-        <v>27.463721714</v>
+        <v>27.324075333</v>
       </c>
       <c r="Q8">
-        <v>28.067721714</v>
+        <v>27.928075333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1036751099174577</v>
+        <v>0.1042088799057376</v>
       </c>
       <c r="T8">
-        <v>0.7543066970400631</v>
+        <v>0.7612635093452622</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.77769835176275</v>
+        <v>28.95231287293951</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2245,22 +2245,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09990710831233598</v>
+        <v>0.09979431330226171</v>
       </c>
       <c r="C9">
-        <v>306.2871507863767</v>
+        <v>303.3551144594077</v>
       </c>
       <c r="D9">
-        <v>264.0505507863767</v>
+        <v>264.3847144594077</v>
       </c>
       <c r="E9">
-        <v>21.1434</v>
+        <v>24.4096</v>
       </c>
       <c r="F9">
-        <v>22.8634</v>
+        <v>26.1296</v>
       </c>
       <c r="G9">
         <v>65.09999999999999</v>
@@ -2281,28 +2281,28 @@
         <v>33.296</v>
       </c>
       <c r="M9">
-        <v>1.15002902</v>
+        <v>1.31431888</v>
       </c>
       <c r="N9">
-        <v>32.14597098</v>
+        <v>31.98168112</v>
       </c>
       <c r="O9">
-        <v>4.821895647</v>
+        <v>4.797252168</v>
       </c>
       <c r="P9">
-        <v>27.324075333</v>
+        <v>27.184428952</v>
       </c>
       <c r="Q9">
-        <v>27.928075333</v>
+        <v>27.788428952</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1042088799057376</v>
+        <v>0.1047542535894149</v>
       </c>
       <c r="T9">
-        <v>0.7612635093452622</v>
+        <v>0.7683715567005742</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.9523128729395</v>
+        <v>25.33327376382207</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2327,22 +2327,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09979431330226171</v>
+        <v>0.09968151829218741</v>
       </c>
       <c r="C10">
-        <v>303.3551144594077</v>
+        <v>300.4239249919123</v>
       </c>
       <c r="D10">
-        <v>264.3847144594077</v>
+        <v>264.7197249919122</v>
       </c>
       <c r="E10">
-        <v>24.4096</v>
+        <v>27.6758</v>
       </c>
       <c r="F10">
-        <v>26.1296</v>
+        <v>29.3958</v>
       </c>
       <c r="G10">
         <v>65.09999999999999</v>
@@ -2363,28 +2363,28 @@
         <v>33.296</v>
       </c>
       <c r="M10">
-        <v>1.31431888</v>
+        <v>1.47860874</v>
       </c>
       <c r="N10">
-        <v>31.98168112</v>
+        <v>31.81739126</v>
       </c>
       <c r="O10">
-        <v>4.797252168</v>
+        <v>4.772608689</v>
       </c>
       <c r="P10">
-        <v>27.184428952</v>
+        <v>27.044782571</v>
       </c>
       <c r="Q10">
-        <v>27.788428952</v>
+        <v>27.648782571</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1047542535894149</v>
+        <v>0.1053116135078982</v>
       </c>
       <c r="T10">
-        <v>0.7683715567005742</v>
+        <v>0.775635824876882</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.33327376382207</v>
+        <v>22.51846556784184</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09968151829218741</v>
+        <v>0.09956872328211314</v>
       </c>
       <c r="C11">
-        <v>300.4239249919123</v>
+        <v>297.4935856072247</v>
       </c>
       <c r="D11">
-        <v>264.7197249919122</v>
+        <v>265.0555856072247</v>
       </c>
       <c r="E11">
-        <v>27.6758</v>
+        <v>30.942</v>
       </c>
       <c r="F11">
-        <v>29.3958</v>
+        <v>32.662</v>
       </c>
       <c r="G11">
         <v>65.09999999999999</v>
@@ -2445,28 +2445,28 @@
         <v>33.296</v>
       </c>
       <c r="M11">
-        <v>1.47860874</v>
+        <v>1.6428986</v>
       </c>
       <c r="N11">
-        <v>31.81739126</v>
+        <v>31.6531014</v>
       </c>
       <c r="O11">
-        <v>4.772608689</v>
+        <v>4.74796521</v>
       </c>
       <c r="P11">
-        <v>27.044782571</v>
+        <v>26.90513619</v>
       </c>
       <c r="Q11">
-        <v>27.648782571</v>
+        <v>27.50913619</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1053116135078982</v>
+        <v>0.1058813592023479</v>
       </c>
       <c r="T11">
-        <v>0.775635824876882</v>
+        <v>0.7830615212348857</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.51846556784184</v>
+        <v>20.26661901105765</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2491,22 +2491,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09956872328211314</v>
+        <v>0.09945592827203885</v>
       </c>
       <c r="C12">
-        <v>297.4935856072247</v>
+        <v>294.5640995450589</v>
       </c>
       <c r="D12">
-        <v>265.0555856072247</v>
+        <v>265.3922995450589</v>
       </c>
       <c r="E12">
-        <v>30.942</v>
+        <v>34.20820000000001</v>
       </c>
       <c r="F12">
-        <v>32.662</v>
+        <v>35.9282</v>
       </c>
       <c r="G12">
         <v>65.09999999999999</v>
@@ -2527,28 +2527,28 @@
         <v>33.296</v>
       </c>
       <c r="M12">
-        <v>1.6428986</v>
+        <v>1.80718846</v>
       </c>
       <c r="N12">
-        <v>31.6531014</v>
+        <v>31.48881154</v>
       </c>
       <c r="O12">
-        <v>4.74796521</v>
+        <v>4.723321731</v>
       </c>
       <c r="P12">
-        <v>26.90513619</v>
+        <v>26.765489809</v>
       </c>
       <c r="Q12">
-        <v>27.50913619</v>
+        <v>27.369489809</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1058813592023479</v>
+        <v>0.1064639081708302</v>
       </c>
       <c r="T12">
-        <v>0.7830615212348857</v>
+        <v>0.790654087173968</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.26661901105765</v>
+        <v>18.4241991009615</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2573,22 +2573,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09945592827203885</v>
+        <v>0.09934313326196456</v>
       </c>
       <c r="C13">
-        <v>294.5640995450589</v>
+        <v>291.6354700616116</v>
       </c>
       <c r="D13">
-        <v>265.3922995450589</v>
+        <v>265.7298700616116</v>
       </c>
       <c r="E13">
-        <v>34.20820000000001</v>
+        <v>37.4744</v>
       </c>
       <c r="F13">
-        <v>35.9282</v>
+        <v>39.1944</v>
       </c>
       <c r="G13">
         <v>65.09999999999999</v>
@@ -2609,28 +2609,28 @@
         <v>33.296</v>
       </c>
       <c r="M13">
-        <v>1.80718846</v>
+        <v>1.97147832</v>
       </c>
       <c r="N13">
-        <v>31.48881154</v>
+        <v>31.32452168</v>
       </c>
       <c r="O13">
-        <v>4.723321731</v>
+        <v>4.698678252</v>
       </c>
       <c r="P13">
-        <v>26.765489809</v>
+        <v>26.625843428</v>
       </c>
       <c r="Q13">
-        <v>27.369489809</v>
+        <v>27.229843428</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1064639081708302</v>
+        <v>0.1070596968885961</v>
       </c>
       <c r="T13">
-        <v>0.790654087173968</v>
+        <v>0.7984192114298477</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.4241991009615</v>
+        <v>16.88884917588138</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2655,22 +2655,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09934313326196456</v>
+        <v>0.09923033825189027</v>
       </c>
       <c r="C14">
-        <v>291.6354700616116</v>
+        <v>288.707700429668</v>
       </c>
       <c r="D14">
-        <v>265.7298700616116</v>
+        <v>266.0683004296679</v>
       </c>
       <c r="E14">
-        <v>37.4744</v>
+        <v>40.7406</v>
       </c>
       <c r="F14">
-        <v>39.1944</v>
+        <v>42.4606</v>
       </c>
       <c r="G14">
         <v>65.09999999999999</v>
@@ -2691,28 +2691,28 @@
         <v>33.296</v>
       </c>
       <c r="M14">
-        <v>1.97147832</v>
+        <v>2.13576818</v>
       </c>
       <c r="N14">
-        <v>31.32452168</v>
+        <v>31.16023182</v>
       </c>
       <c r="O14">
-        <v>4.698678252</v>
+        <v>4.674034773</v>
       </c>
       <c r="P14">
-        <v>26.625843428</v>
+        <v>26.486197047</v>
       </c>
       <c r="Q14">
-        <v>27.229843428</v>
+        <v>27.090197047</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1070596968885961</v>
+        <v>0.1076691818987245</v>
       </c>
       <c r="T14">
-        <v>0.7984192114298477</v>
+        <v>0.8063628442893107</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.88884917588138</v>
+        <v>15.58970693158281</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2737,22 +2737,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09923033825189027</v>
+        <v>0.09911754324181599</v>
       </c>
       <c r="C15">
-        <v>288.707700429668</v>
+        <v>285.7807939387069</v>
       </c>
       <c r="D15">
-        <v>266.0683004296679</v>
+        <v>266.4075939387069</v>
       </c>
       <c r="E15">
-        <v>40.7406</v>
+        <v>44.00680000000001</v>
       </c>
       <c r="F15">
-        <v>42.4606</v>
+        <v>45.7268</v>
       </c>
       <c r="G15">
         <v>65.09999999999999</v>
@@ -2773,28 +2773,28 @@
         <v>33.296</v>
       </c>
       <c r="M15">
-        <v>2.13576818</v>
+        <v>2.30005804</v>
       </c>
       <c r="N15">
-        <v>31.16023182</v>
+        <v>30.99594196</v>
       </c>
       <c r="O15">
-        <v>4.674034773</v>
+        <v>4.649391294</v>
       </c>
       <c r="P15">
-        <v>26.486197047</v>
+        <v>26.346550666</v>
       </c>
       <c r="Q15">
-        <v>27.090197047</v>
+        <v>26.950550666</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1076691818987245</v>
+        <v>0.1082928409788558</v>
       </c>
       <c r="T15">
-        <v>0.8063628442893107</v>
+        <v>0.8144912127966683</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.58970693158281</v>
+        <v>14.47615643646975</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2819,22 +2819,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09911754324181599</v>
+        <v>0.0990047482317417</v>
       </c>
       <c r="C16">
-        <v>285.7807939387069</v>
+        <v>282.8547538950082</v>
       </c>
       <c r="D16">
-        <v>266.4075939387069</v>
+        <v>266.7477538950081</v>
       </c>
       <c r="E16">
-        <v>44.00680000000001</v>
+        <v>47.27300000000001</v>
       </c>
       <c r="F16">
-        <v>45.7268</v>
+        <v>48.99300000000001</v>
       </c>
       <c r="G16">
         <v>65.09999999999999</v>
@@ -2855,28 +2855,28 @@
         <v>33.296</v>
       </c>
       <c r="M16">
-        <v>2.30005804</v>
+        <v>2.4643479</v>
       </c>
       <c r="N16">
-        <v>30.99594196</v>
+        <v>30.8316521</v>
       </c>
       <c r="O16">
-        <v>4.649391294</v>
+        <v>4.624747815</v>
       </c>
       <c r="P16">
-        <v>26.346550666</v>
+        <v>26.206904285</v>
       </c>
       <c r="Q16">
-        <v>26.950550666</v>
+        <v>26.810904285</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1082928409788558</v>
+        <v>0.1089311743902844</v>
       </c>
       <c r="T16">
-        <v>0.8144912127966683</v>
+        <v>0.8228108370336108</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.47615643646975</v>
+        <v>13.5110793407051</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2901,22 +2901,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0990047482317417</v>
+        <v>0.09909595322166743</v>
       </c>
       <c r="C17">
-        <v>282.8547538950082</v>
+        <v>279.3134365839064</v>
       </c>
       <c r="D17">
-        <v>266.7477538950081</v>
+        <v>266.4726365839064</v>
       </c>
       <c r="E17">
-        <v>47.273</v>
+        <v>50.5392</v>
       </c>
       <c r="F17">
-        <v>48.993</v>
+        <v>52.2592</v>
       </c>
       <c r="G17">
         <v>65.09999999999999</v>
@@ -2937,45 +2937,45 @@
         <v>33.296</v>
       </c>
       <c r="M17">
-        <v>2.4643479</v>
+        <v>2.70702656</v>
       </c>
       <c r="N17">
-        <v>30.8316521</v>
+        <v>30.58897344</v>
       </c>
       <c r="O17">
-        <v>4.624747815</v>
+        <v>4.588346016</v>
       </c>
       <c r="P17">
-        <v>26.206904285</v>
+        <v>26.000627424</v>
       </c>
       <c r="Q17">
-        <v>26.810904285</v>
+        <v>26.604627424</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1089311743902844</v>
+        <v>0.1095847062162708</v>
       </c>
       <c r="T17">
-        <v>0.8228108370336108</v>
+        <v>0.8313285475619091</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.5110793407051</v>
+        <v>12.29984237760859</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2983,22 +2983,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09909595322166743</v>
+        <v>0.09899590821159313</v>
       </c>
       <c r="C18">
-        <v>279.3134365839064</v>
+        <v>276.3490497716709</v>
       </c>
       <c r="D18">
-        <v>266.4726365839064</v>
+        <v>266.774449771671</v>
       </c>
       <c r="E18">
-        <v>50.5392</v>
+        <v>53.80540000000001</v>
       </c>
       <c r="F18">
-        <v>52.2592</v>
+        <v>55.5254</v>
       </c>
       <c r="G18">
         <v>65.09999999999999</v>
@@ -3019,28 +3019,28 @@
         <v>33.296</v>
       </c>
       <c r="M18">
-        <v>2.70702656</v>
+        <v>2.87621572</v>
       </c>
       <c r="N18">
-        <v>30.58897344</v>
+        <v>30.41978428</v>
       </c>
       <c r="O18">
-        <v>4.588346016</v>
+        <v>4.562967641999999</v>
       </c>
       <c r="P18">
-        <v>26.000627424</v>
+        <v>25.856816638</v>
       </c>
       <c r="Q18">
-        <v>26.604627424</v>
+        <v>26.460816638</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1095847062162708</v>
+        <v>0.1102539857971002</v>
       </c>
       <c r="T18">
-        <v>0.8313285475619091</v>
+        <v>0.8400515041270338</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.29984237760859</v>
+        <v>11.57632223774926</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3065,22 +3065,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09899590821159313</v>
+        <v>0.09889586320151884</v>
       </c>
       <c r="C19">
-        <v>276.3490497716709</v>
+        <v>273.3853474161249</v>
       </c>
       <c r="D19">
-        <v>266.774449771671</v>
+        <v>267.0769474161249</v>
       </c>
       <c r="E19">
-        <v>53.80540000000001</v>
+        <v>57.07160000000001</v>
       </c>
       <c r="F19">
-        <v>55.5254</v>
+        <v>58.79160000000001</v>
       </c>
       <c r="G19">
         <v>65.09999999999999</v>
@@ -3101,28 +3101,28 @@
         <v>33.296</v>
       </c>
       <c r="M19">
-        <v>2.87621572</v>
+        <v>3.04540488</v>
       </c>
       <c r="N19">
-        <v>30.41978428</v>
+        <v>30.25059512</v>
       </c>
       <c r="O19">
-        <v>4.562967641999999</v>
+        <v>4.537589268</v>
       </c>
       <c r="P19">
-        <v>25.856816638</v>
+        <v>25.713005852</v>
       </c>
       <c r="Q19">
-        <v>26.460816638</v>
+        <v>26.317005852</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1102539857971002</v>
+        <v>0.1109395892701449</v>
       </c>
       <c r="T19">
-        <v>0.8400515041270338</v>
+        <v>0.8489872157303322</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.57632223774926</v>
+        <v>10.93319322454097</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09889586320151886</v>
+        <v>0.09879581819144458</v>
       </c>
       <c r="C20">
-        <v>273.3853474161249</v>
+        <v>270.4223318482439</v>
       </c>
       <c r="D20">
-        <v>267.0769474161249</v>
+        <v>267.3801318482439</v>
       </c>
       <c r="E20">
-        <v>57.0716</v>
+        <v>60.3378</v>
       </c>
       <c r="F20">
-        <v>58.7916</v>
+        <v>62.0578</v>
       </c>
       <c r="G20">
         <v>65.09999999999999</v>
@@ -3183,28 +3183,28 @@
         <v>33.296</v>
       </c>
       <c r="M20">
-        <v>3.04540488</v>
+        <v>3.21459404</v>
       </c>
       <c r="N20">
-        <v>30.25059512</v>
+        <v>30.08140596</v>
       </c>
       <c r="O20">
-        <v>4.537589268</v>
+        <v>4.512210894</v>
       </c>
       <c r="P20">
-        <v>25.713005852</v>
+        <v>25.569195066</v>
       </c>
       <c r="Q20">
-        <v>26.317005852</v>
+        <v>26.173195066</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1109395892701449</v>
+        <v>0.1116421212240056</v>
       </c>
       <c r="T20">
-        <v>0.8489872157303322</v>
+        <v>0.8581435621880331</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.93319322454097</v>
+        <v>10.35776200219671</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3229,22 +3229,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09879581819144458</v>
+        <v>0.09869577318137028</v>
       </c>
       <c r="C21">
-        <v>270.4223318482439</v>
+        <v>267.4600054096001</v>
       </c>
       <c r="D21">
-        <v>267.3801318482439</v>
+        <v>267.6840054096001</v>
       </c>
       <c r="E21">
-        <v>60.3378</v>
+        <v>63.604</v>
       </c>
       <c r="F21">
-        <v>62.0578</v>
+        <v>65.324</v>
       </c>
       <c r="G21">
         <v>65.09999999999999</v>
@@ -3265,28 +3265,28 @@
         <v>33.296</v>
       </c>
       <c r="M21">
-        <v>3.21459404</v>
+        <v>3.3837832</v>
       </c>
       <c r="N21">
-        <v>30.08140596</v>
+        <v>29.9122168</v>
       </c>
       <c r="O21">
-        <v>4.512210894</v>
+        <v>4.48683252</v>
       </c>
       <c r="P21">
-        <v>25.569195066</v>
+        <v>25.42538428</v>
       </c>
       <c r="Q21">
-        <v>26.173195066</v>
+        <v>26.02938428</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1116421212240056</v>
+        <v>0.1123622164767129</v>
       </c>
       <c r="T21">
-        <v>0.8581435621880331</v>
+        <v>0.8675288173071766</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.35776200219671</v>
+        <v>9.839873902086872</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3311,22 +3311,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09869577318137028</v>
+        <v>0.09889917817129601</v>
       </c>
       <c r="C22">
-        <v>267.4600054096001</v>
+        <v>263.5767132337055</v>
       </c>
       <c r="D22">
-        <v>267.6840054096001</v>
+        <v>267.0669132337055</v>
       </c>
       <c r="E22">
-        <v>63.604</v>
+        <v>66.87020000000001</v>
       </c>
       <c r="F22">
-        <v>65.324</v>
+        <v>68.59020000000001</v>
       </c>
       <c r="G22">
         <v>65.09999999999999</v>
@@ -3347,45 +3347,45 @@
         <v>33.296</v>
       </c>
       <c r="M22">
-        <v>3.3837832</v>
+        <v>3.669575700000001</v>
       </c>
       <c r="N22">
-        <v>29.9122168</v>
+        <v>29.6264243</v>
       </c>
       <c r="O22">
-        <v>4.48683252</v>
+        <v>4.443963645</v>
       </c>
       <c r="P22">
-        <v>25.42538428</v>
+        <v>25.182460655</v>
       </c>
       <c r="Q22">
-        <v>26.02938428</v>
+        <v>25.786460655</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1123622164767129</v>
+        <v>0.1131005419889823</v>
       </c>
       <c r="T22">
-        <v>0.8675288173071766</v>
+        <v>0.8771516738217415</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.15</v>
       </c>
       <c r="W22">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.839873902086872</v>
+        <v>9.073528582609699</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3393,22 +3393,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09889917817129601</v>
+        <v>0.09881358316122173</v>
       </c>
       <c r="C23">
-        <v>263.5767132337055</v>
+        <v>260.5698452047751</v>
       </c>
       <c r="D23">
-        <v>267.0669132337055</v>
+        <v>267.3262452047751</v>
       </c>
       <c r="E23">
-        <v>66.8702</v>
+        <v>70.13640000000001</v>
       </c>
       <c r="F23">
-        <v>68.5902</v>
+        <v>71.85640000000001</v>
       </c>
       <c r="G23">
         <v>65.09999999999999</v>
@@ -3429,28 +3429,28 @@
         <v>33.296</v>
       </c>
       <c r="M23">
-        <v>3.6695757</v>
+        <v>3.8443174</v>
       </c>
       <c r="N23">
-        <v>29.6264243</v>
+        <v>29.4516826</v>
       </c>
       <c r="O23">
-        <v>4.443963645</v>
+        <v>4.41775239</v>
       </c>
       <c r="P23">
-        <v>25.182460655</v>
+        <v>25.03393021</v>
       </c>
       <c r="Q23">
-        <v>25.786460655</v>
+        <v>25.63793021</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1131005419889823</v>
+        <v>0.1138577989246432</v>
       </c>
       <c r="T23">
-        <v>0.8771516738217413</v>
+        <v>0.8870212702469361</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.073528582609701</v>
+        <v>8.661095465218349</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3475,22 +3475,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09881358316122173</v>
+        <v>0.09872798815114744</v>
       </c>
       <c r="C24">
-        <v>260.5698452047751</v>
+        <v>257.5634813074807</v>
       </c>
       <c r="D24">
-        <v>267.3262452047751</v>
+        <v>267.5860813074808</v>
       </c>
       <c r="E24">
-        <v>70.13640000000001</v>
+        <v>73.40260000000001</v>
       </c>
       <c r="F24">
-        <v>71.85640000000001</v>
+        <v>75.12260000000001</v>
       </c>
       <c r="G24">
         <v>65.09999999999999</v>
@@ -3511,28 +3511,28 @@
         <v>33.296</v>
       </c>
       <c r="M24">
-        <v>3.8443174</v>
+        <v>4.019059100000001</v>
       </c>
       <c r="N24">
-        <v>29.4516826</v>
+        <v>29.2769409</v>
       </c>
       <c r="O24">
-        <v>4.41775239</v>
+        <v>4.391541135</v>
       </c>
       <c r="P24">
-        <v>25.03393021</v>
+        <v>24.885399765</v>
       </c>
       <c r="Q24">
-        <v>25.63793021</v>
+        <v>25.489399765</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1138577989246432</v>
+        <v>0.11463472487162</v>
       </c>
       <c r="T24">
-        <v>0.8870212702469361</v>
+        <v>0.8971472198260318</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.661095465218349</v>
+        <v>8.284526097165378</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3557,22 +3557,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09872798815114744</v>
+        <v>0.09864239314107315</v>
       </c>
       <c r="C25">
-        <v>257.5634813074807</v>
+        <v>254.5576230132722</v>
       </c>
       <c r="D25">
-        <v>267.5860813074808</v>
+        <v>267.8464230132722</v>
       </c>
       <c r="E25">
-        <v>73.40260000000001</v>
+        <v>76.6688</v>
       </c>
       <c r="F25">
-        <v>75.12260000000001</v>
+        <v>78.3888</v>
       </c>
       <c r="G25">
         <v>65.09999999999999</v>
@@ -3593,28 +3593,28 @@
         <v>33.296</v>
       </c>
       <c r="M25">
-        <v>4.019059100000001</v>
+        <v>4.1938008</v>
       </c>
       <c r="N25">
-        <v>29.2769409</v>
+        <v>29.1021992</v>
       </c>
       <c r="O25">
-        <v>4.391541135</v>
+        <v>4.36532988</v>
       </c>
       <c r="P25">
-        <v>24.885399765</v>
+        <v>24.73686932</v>
       </c>
       <c r="Q25">
-        <v>25.489399765</v>
+        <v>25.34086932</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.11463472487162</v>
+        <v>0.1154320962382542</v>
       </c>
       <c r="T25">
-        <v>0.8971472198260318</v>
+        <v>0.9075396417624724</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.284526097165378</v>
+        <v>7.939337509783488</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3639,22 +3639,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09864239314107315</v>
+        <v>0.09855679813099885</v>
       </c>
       <c r="C26">
-        <v>254.5576230132722</v>
+        <v>251.5522717993311</v>
       </c>
       <c r="D26">
-        <v>267.8464230132722</v>
+        <v>268.1072717993312</v>
       </c>
       <c r="E26">
-        <v>76.6688</v>
+        <v>79.935</v>
       </c>
       <c r="F26">
-        <v>78.3888</v>
+        <v>81.655</v>
       </c>
       <c r="G26">
         <v>65.09999999999999</v>
@@ -3675,28 +3675,28 @@
         <v>33.296</v>
       </c>
       <c r="M26">
-        <v>4.1938008</v>
+        <v>4.3685425</v>
       </c>
       <c r="N26">
-        <v>29.1021992</v>
+        <v>28.9274575</v>
       </c>
       <c r="O26">
-        <v>4.36532988</v>
+        <v>4.339118624999999</v>
       </c>
       <c r="P26">
-        <v>24.73686932</v>
+        <v>24.588338875</v>
       </c>
       <c r="Q26">
-        <v>25.34086932</v>
+        <v>25.192338875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1154320962382542</v>
+        <v>0.1162507308413318</v>
       </c>
       <c r="T26">
-        <v>0.9075396417624724</v>
+        <v>0.9182091949505511</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.939337509783488</v>
+        <v>7.621764009392148</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3721,22 +3721,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09855679813099885</v>
+        <v>0.09864800312092459</v>
       </c>
       <c r="C27">
-        <v>251.5522717993311</v>
+        <v>248.0081444536995</v>
       </c>
       <c r="D27">
-        <v>268.1072717993312</v>
+        <v>267.8293444536995</v>
       </c>
       <c r="E27">
-        <v>79.935</v>
+        <v>83.2012</v>
       </c>
       <c r="F27">
-        <v>81.655</v>
+        <v>84.9212</v>
       </c>
       <c r="G27">
         <v>65.09999999999999</v>
@@ -3757,45 +3757,45 @@
         <v>33.296</v>
       </c>
       <c r="M27">
-        <v>4.3685425</v>
+        <v>4.61122116</v>
       </c>
       <c r="N27">
-        <v>28.9274575</v>
+        <v>28.68477884</v>
       </c>
       <c r="O27">
-        <v>4.339118624999999</v>
+        <v>4.302716826</v>
       </c>
       <c r="P27">
-        <v>24.588338875</v>
+        <v>24.382062014</v>
       </c>
       <c r="Q27">
-        <v>25.192338875</v>
+        <v>24.986062014</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1162507308413318</v>
+        <v>0.1170914907039521</v>
       </c>
       <c r="T27">
-        <v>0.9182091949505511</v>
+        <v>0.9291671144410105</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.15</v>
       </c>
       <c r="W27">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.621764009392148</v>
+        <v>7.220646948974357</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3803,22 +3803,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09864800312092459</v>
+        <v>0.09856920811085031</v>
       </c>
       <c r="C28">
-        <v>248.0081444536995</v>
+        <v>244.9820211900562</v>
       </c>
       <c r="D28">
-        <v>267.8293444536995</v>
+        <v>268.0694211900562</v>
       </c>
       <c r="E28">
-        <v>83.2012</v>
+        <v>86.46740000000001</v>
       </c>
       <c r="F28">
-        <v>84.9212</v>
+        <v>88.18740000000001</v>
       </c>
       <c r="G28">
         <v>65.09999999999999</v>
@@ -3839,28 +3839,28 @@
         <v>33.296</v>
       </c>
       <c r="M28">
-        <v>4.61122116</v>
+        <v>4.788575820000001</v>
       </c>
       <c r="N28">
-        <v>28.68477884</v>
+        <v>28.50742418</v>
       </c>
       <c r="O28">
-        <v>4.302716826</v>
+        <v>4.276113626999999</v>
       </c>
       <c r="P28">
-        <v>24.382062014</v>
+        <v>24.231310553</v>
       </c>
       <c r="Q28">
-        <v>24.986062014</v>
+        <v>24.835310553</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1170914907039521</v>
+        <v>0.1179552850833566</v>
       </c>
       <c r="T28">
-        <v>0.9291671144410105</v>
+        <v>0.9404252509038113</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.220646948974357</v>
+        <v>6.953215580493825</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3885,22 +3885,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09856920811085031</v>
+        <v>0.09849041310077601</v>
       </c>
       <c r="C29">
-        <v>244.9820211900562</v>
+        <v>241.9563287122948</v>
       </c>
       <c r="D29">
-        <v>268.0694211900562</v>
+        <v>268.3099287122948</v>
       </c>
       <c r="E29">
-        <v>86.46740000000001</v>
+        <v>89.73360000000001</v>
       </c>
       <c r="F29">
-        <v>88.18740000000001</v>
+        <v>91.45360000000001</v>
       </c>
       <c r="G29">
         <v>65.09999999999999</v>
@@ -3921,28 +3921,28 @@
         <v>33.296</v>
       </c>
       <c r="M29">
-        <v>4.788575820000001</v>
+        <v>4.965930480000001</v>
       </c>
       <c r="N29">
-        <v>28.50742418</v>
+        <v>28.33006952</v>
       </c>
       <c r="O29">
-        <v>4.276113626999999</v>
+        <v>4.249510428</v>
       </c>
       <c r="P29">
-        <v>24.231310553</v>
+        <v>24.080559092</v>
       </c>
       <c r="Q29">
-        <v>24.835310553</v>
+        <v>24.684559092</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1179552850833566</v>
+        <v>0.1188430737510778</v>
       </c>
       <c r="T29">
-        <v>0.9404252509038113</v>
+        <v>0.9519961133794678</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.953215580493825</v>
+        <v>6.704886452619045</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3967,22 +3967,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09849041310077601</v>
+        <v>0.09841161809070174</v>
       </c>
       <c r="C30">
-        <v>241.9563287122948</v>
+        <v>238.9310681809388</v>
       </c>
       <c r="D30">
-        <v>268.3099287122948</v>
+        <v>268.5508681809388</v>
       </c>
       <c r="E30">
-        <v>89.73360000000001</v>
+        <v>92.99980000000001</v>
       </c>
       <c r="F30">
-        <v>91.45360000000001</v>
+        <v>94.71980000000001</v>
       </c>
       <c r="G30">
         <v>65.09999999999999</v>
@@ -4003,28 +4003,28 @@
         <v>33.296</v>
       </c>
       <c r="M30">
-        <v>4.965930480000001</v>
+        <v>5.143285140000001</v>
       </c>
       <c r="N30">
-        <v>28.33006952</v>
+        <v>28.15271486</v>
       </c>
       <c r="O30">
-        <v>4.249510428</v>
+        <v>4.222907229</v>
       </c>
       <c r="P30">
-        <v>24.080559092</v>
+        <v>23.929807631</v>
       </c>
       <c r="Q30">
-        <v>24.684559092</v>
+        <v>24.533807631</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1188430737510778</v>
+        <v>0.1197558705502841</v>
       </c>
       <c r="T30">
-        <v>0.9519961133794678</v>
+        <v>0.9638929156431706</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.704886452619045</v>
+        <v>6.473683471494251</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4049,22 +4049,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09841161809070173</v>
+        <v>0.09833282308062745</v>
       </c>
       <c r="C31">
-        <v>238.9310681809388</v>
+        <v>235.9062407606839</v>
       </c>
       <c r="D31">
-        <v>268.5508681809388</v>
+        <v>268.7922407606839</v>
       </c>
       <c r="E31">
-        <v>92.99979999999999</v>
+        <v>96.26600000000001</v>
       </c>
       <c r="F31">
-        <v>94.71979999999999</v>
+        <v>97.986</v>
       </c>
       <c r="G31">
         <v>65.09999999999999</v>
@@ -4085,28 +4085,28 @@
         <v>33.296</v>
       </c>
       <c r="M31">
-        <v>5.14328514</v>
+        <v>5.3206398</v>
       </c>
       <c r="N31">
-        <v>28.15271486</v>
+        <v>27.9753602</v>
       </c>
       <c r="O31">
-        <v>4.222907229</v>
+        <v>4.196304029999999</v>
       </c>
       <c r="P31">
-        <v>23.929807631</v>
+        <v>23.77905617</v>
       </c>
       <c r="Q31">
-        <v>24.533807631</v>
+        <v>24.38305617</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1197558705502841</v>
+        <v>0.1206947472580392</v>
       </c>
       <c r="T31">
-        <v>0.9638929156431706</v>
+        <v>0.9761296265429793</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.473683471494252</v>
+        <v>6.257894022444443</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4131,22 +4131,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09833282308062745</v>
+        <v>0.09851752807055317</v>
       </c>
       <c r="C32">
-        <v>235.9062407606839</v>
+        <v>232.0749164826727</v>
       </c>
       <c r="D32">
-        <v>268.7922407606839</v>
+        <v>268.2271164826728</v>
       </c>
       <c r="E32">
-        <v>96.26600000000001</v>
+        <v>99.5322</v>
       </c>
       <c r="F32">
-        <v>97.986</v>
+        <v>101.2522</v>
       </c>
       <c r="G32">
         <v>65.09999999999999</v>
@@ -4167,45 +4167,45 @@
         <v>33.296</v>
       </c>
       <c r="M32">
-        <v>5.3206398</v>
+        <v>5.59924666</v>
       </c>
       <c r="N32">
-        <v>27.9753602</v>
+        <v>27.69675334</v>
       </c>
       <c r="O32">
-        <v>4.196304029999999</v>
+        <v>4.154513001</v>
       </c>
       <c r="P32">
-        <v>23.77905617</v>
+        <v>23.542240339</v>
       </c>
       <c r="Q32">
-        <v>24.38305617</v>
+        <v>24.146240339</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1206947472580392</v>
+        <v>0.1216608377834104</v>
       </c>
       <c r="T32">
-        <v>0.9761296265429793</v>
+        <v>0.9887210247152464</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.257894022444443</v>
+        <v>5.946514240542495</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09851752807055317</v>
+        <v>0.09844723306047887</v>
       </c>
       <c r="C33">
-        <v>232.0749164826727</v>
+        <v>229.0235111171701</v>
       </c>
       <c r="D33">
-        <v>268.2271164826728</v>
+        <v>268.4419111171702</v>
       </c>
       <c r="E33">
-        <v>99.5322</v>
+        <v>102.7984</v>
       </c>
       <c r="F33">
-        <v>101.2522</v>
+        <v>104.5184</v>
       </c>
       <c r="G33">
         <v>65.09999999999999</v>
@@ -4249,28 +4249,28 @@
         <v>33.296</v>
       </c>
       <c r="M33">
-        <v>5.59924666</v>
+        <v>5.77986752</v>
       </c>
       <c r="N33">
-        <v>27.69675334</v>
+        <v>27.51613248</v>
       </c>
       <c r="O33">
-        <v>4.154513001</v>
+        <v>4.127419872</v>
       </c>
       <c r="P33">
-        <v>23.542240339</v>
+        <v>23.388712608</v>
       </c>
       <c r="Q33">
-        <v>24.146240339</v>
+        <v>23.992712608</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1216608377834104</v>
+        <v>0.1226553427359983</v>
       </c>
       <c r="T33">
-        <v>0.9887210247152464</v>
+        <v>1.001682758127874</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.946514240542495</v>
+        <v>5.760685670525541</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4295,22 +4295,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09844723306047887</v>
+        <v>0.09837693805040459</v>
       </c>
       <c r="C34">
-        <v>229.0235111171701</v>
+        <v>225.9724500398307</v>
       </c>
       <c r="D34">
-        <v>268.4419111171702</v>
+        <v>268.6570500398307</v>
       </c>
       <c r="E34">
-        <v>102.7984</v>
+        <v>106.0646</v>
       </c>
       <c r="F34">
-        <v>104.5184</v>
+        <v>107.7846</v>
       </c>
       <c r="G34">
         <v>65.09999999999999</v>
@@ -4331,28 +4331,28 @@
         <v>33.296</v>
       </c>
       <c r="M34">
-        <v>5.77986752</v>
+        <v>5.960488380000001</v>
       </c>
       <c r="N34">
-        <v>27.51613248</v>
+        <v>27.33551162</v>
       </c>
       <c r="O34">
-        <v>4.127419872</v>
+        <v>4.100326742999999</v>
       </c>
       <c r="P34">
-        <v>23.388712608</v>
+        <v>23.235184877</v>
       </c>
       <c r="Q34">
-        <v>23.992712608</v>
+        <v>23.839184877</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1226553427359983</v>
+        <v>0.1236795344035889</v>
       </c>
       <c r="T34">
-        <v>1.001682758127874</v>
+        <v>1.015031408955804</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.760685670525541</v>
+        <v>5.586119438085372</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4377,22 +4377,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09837693805040459</v>
+        <v>0.09830664304033031</v>
       </c>
       <c r="C35">
-        <v>225.9724500398307</v>
+        <v>222.9217340790929</v>
       </c>
       <c r="D35">
-        <v>268.6570500398307</v>
+        <v>268.8725340790929</v>
       </c>
       <c r="E35">
-        <v>106.0646</v>
+        <v>109.3308</v>
       </c>
       <c r="F35">
-        <v>107.7846</v>
+        <v>111.0508</v>
       </c>
       <c r="G35">
         <v>65.09999999999999</v>
@@ -4413,28 +4413,28 @@
         <v>33.296</v>
       </c>
       <c r="M35">
-        <v>5.960488380000001</v>
+        <v>6.14110924</v>
       </c>
       <c r="N35">
-        <v>27.33551162</v>
+        <v>27.15489076</v>
       </c>
       <c r="O35">
-        <v>4.100326742999999</v>
+        <v>4.073233614</v>
       </c>
       <c r="P35">
-        <v>23.235184877</v>
+        <v>23.081657146</v>
       </c>
       <c r="Q35">
-        <v>23.839184877</v>
+        <v>23.685657146</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1236795344035889</v>
+        <v>0.1247347621823187</v>
       </c>
       <c r="T35">
-        <v>1.015031408955804</v>
+        <v>1.028784564354278</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.586119438085372</v>
+        <v>5.421821807553451</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4459,22 +4459,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09830664304033031</v>
+        <v>0.09823634803025602</v>
       </c>
       <c r="C36">
-        <v>222.9217340790929</v>
+        <v>219.8713640660552</v>
       </c>
       <c r="D36">
-        <v>268.8725340790929</v>
+        <v>269.0883640660552</v>
       </c>
       <c r="E36">
-        <v>109.3308</v>
+        <v>112.597</v>
       </c>
       <c r="F36">
-        <v>111.0508</v>
+        <v>114.317</v>
       </c>
       <c r="G36">
         <v>65.09999999999999</v>
@@ -4495,28 +4495,28 @@
         <v>33.296</v>
       </c>
       <c r="M36">
-        <v>6.14110924</v>
+        <v>6.321730100000001</v>
       </c>
       <c r="N36">
-        <v>27.15489076</v>
+        <v>26.9742699</v>
       </c>
       <c r="O36">
-        <v>4.073233614</v>
+        <v>4.046140485</v>
       </c>
       <c r="P36">
-        <v>23.081657146</v>
+        <v>22.928129415</v>
       </c>
       <c r="Q36">
-        <v>23.685657146</v>
+        <v>23.532129415</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1247347621823187</v>
+        <v>0.1258224585080862</v>
       </c>
       <c r="T36">
-        <v>1.028784564354278</v>
+        <v>1.042960893765012</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.421821807553451</v>
+        <v>5.266912613051923</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4541,22 +4541,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09823634803025602</v>
+        <v>0.09816605302018173</v>
       </c>
       <c r="C37">
-        <v>219.8713640660552</v>
+        <v>216.8213408344866</v>
       </c>
       <c r="D37">
-        <v>269.0883640660552</v>
+        <v>269.3045408344867</v>
       </c>
       <c r="E37">
-        <v>112.597</v>
+        <v>115.8632</v>
       </c>
       <c r="F37">
-        <v>114.317</v>
+        <v>117.5832</v>
       </c>
       <c r="G37">
         <v>65.09999999999999</v>
@@ -4577,28 +4577,28 @@
         <v>33.296</v>
       </c>
       <c r="M37">
-        <v>6.321730100000001</v>
+        <v>6.502350960000001</v>
       </c>
       <c r="N37">
-        <v>26.9742699</v>
+        <v>26.79364904</v>
       </c>
       <c r="O37">
-        <v>4.046140485</v>
+        <v>4.019047356</v>
       </c>
       <c r="P37">
-        <v>22.928129415</v>
+        <v>22.774601684</v>
       </c>
       <c r="Q37">
-        <v>23.532129415</v>
+        <v>23.378601684</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1258224585080862</v>
+        <v>0.126944145344034</v>
       </c>
       <c r="T37">
-        <v>1.042960893765012</v>
+        <v>1.057580233469831</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.266912613051923</v>
+        <v>5.120609484911592</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4623,22 +4623,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09816605302018175</v>
+        <v>0.09809575801010746</v>
       </c>
       <c r="C38">
-        <v>216.8213408344866</v>
+        <v>213.7716652208377</v>
       </c>
       <c r="D38">
-        <v>269.3045408344866</v>
+        <v>269.5210652208377</v>
       </c>
       <c r="E38">
-        <v>115.8632</v>
+        <v>119.1294</v>
       </c>
       <c r="F38">
-        <v>117.5832</v>
+        <v>120.8494</v>
       </c>
       <c r="G38">
         <v>65.09999999999999</v>
@@ -4659,28 +4659,28 @@
         <v>33.296</v>
       </c>
       <c r="M38">
-        <v>6.502350959999999</v>
+        <v>6.682971820000001</v>
       </c>
       <c r="N38">
-        <v>26.79364904</v>
+        <v>26.61302818</v>
       </c>
       <c r="O38">
-        <v>4.019047356</v>
+        <v>3.991954227</v>
       </c>
       <c r="P38">
-        <v>22.774601684</v>
+        <v>22.621073953</v>
       </c>
       <c r="Q38">
-        <v>23.378601684</v>
+        <v>23.225073953</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.126944145344034</v>
+        <v>0.1281014412858849</v>
       </c>
       <c r="T38">
-        <v>1.057580233469831</v>
+        <v>1.072663679197026</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.120609484911593</v>
+        <v>4.982214633968036</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4705,22 +4705,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09809575801010746</v>
+        <v>0.09802546300003318</v>
       </c>
       <c r="C39">
-        <v>213.7716652208377</v>
+        <v>210.7223380642515</v>
       </c>
       <c r="D39">
-        <v>269.5210652208377</v>
+        <v>269.7379380642515</v>
       </c>
       <c r="E39">
-        <v>119.1294</v>
+        <v>122.3956</v>
       </c>
       <c r="F39">
-        <v>120.8494</v>
+        <v>124.1156</v>
       </c>
       <c r="G39">
         <v>65.09999999999999</v>
@@ -4741,28 +4741,28 @@
         <v>33.296</v>
       </c>
       <c r="M39">
-        <v>6.682971820000001</v>
+        <v>6.86359268</v>
       </c>
       <c r="N39">
-        <v>26.61302818</v>
+        <v>26.43240732</v>
       </c>
       <c r="O39">
-        <v>3.991954227</v>
+        <v>3.964861098</v>
       </c>
       <c r="P39">
-        <v>22.621073953</v>
+        <v>22.467546222</v>
       </c>
       <c r="Q39">
-        <v>23.225073953</v>
+        <v>23.071546222</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1281014412858849</v>
+        <v>0.1292960693548922</v>
       </c>
       <c r="T39">
-        <v>1.072663679197026</v>
+        <v>1.088233687689614</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.982214633968036</v>
+        <v>4.851103722547824</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4787,22 +4787,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09802546300003318</v>
+        <v>0.09795516798995889</v>
       </c>
       <c r="C40">
-        <v>210.7223380642515</v>
+        <v>207.6733602065735</v>
       </c>
       <c r="D40">
-        <v>269.7379380642515</v>
+        <v>269.9551602065735</v>
       </c>
       <c r="E40">
-        <v>122.3956</v>
+        <v>125.6618</v>
       </c>
       <c r="F40">
-        <v>124.1156</v>
+        <v>127.3818</v>
       </c>
       <c r="G40">
         <v>65.09999999999999</v>
@@ -4823,28 +4823,28 @@
         <v>33.296</v>
       </c>
       <c r="M40">
-        <v>6.86359268</v>
+        <v>7.044213540000001</v>
       </c>
       <c r="N40">
-        <v>26.43240732</v>
+        <v>26.25178646</v>
       </c>
       <c r="O40">
-        <v>3.964861098</v>
+        <v>3.937767968999999</v>
       </c>
       <c r="P40">
-        <v>22.467546222</v>
+        <v>22.314018491</v>
       </c>
       <c r="Q40">
-        <v>23.071546222</v>
+        <v>22.918018491</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1292960693548922</v>
+        <v>0.1305298655573097</v>
       </c>
       <c r="T40">
-        <v>1.088233687689614</v>
+        <v>1.104314188263927</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.851103722547824</v>
+        <v>4.7267164476107</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4869,22 +4869,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09795516798995889</v>
+        <v>0.0978848729798846</v>
       </c>
       <c r="C41">
-        <v>207.6733602065735</v>
+        <v>204.6247324923637</v>
       </c>
       <c r="D41">
-        <v>269.9551602065735</v>
+        <v>270.1727324923638</v>
       </c>
       <c r="E41">
-        <v>125.6618</v>
+        <v>128.928</v>
       </c>
       <c r="F41">
-        <v>127.3818</v>
+        <v>130.648</v>
       </c>
       <c r="G41">
         <v>65.09999999999999</v>
@@ -4905,28 +4905,28 @@
         <v>33.296</v>
       </c>
       <c r="M41">
-        <v>7.044213540000001</v>
+        <v>7.2248344</v>
       </c>
       <c r="N41">
-        <v>26.25178646</v>
+        <v>26.0711656</v>
       </c>
       <c r="O41">
-        <v>3.937767968999999</v>
+        <v>3.91067484</v>
       </c>
       <c r="P41">
-        <v>22.314018491</v>
+        <v>22.16049076</v>
       </c>
       <c r="Q41">
-        <v>22.918018491</v>
+        <v>22.76449076</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1305298655573097</v>
+        <v>0.1318047882998077</v>
       </c>
       <c r="T41">
-        <v>1.104314188263927</v>
+        <v>1.12093070552405</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.7267164476107</v>
+        <v>4.608548536420434</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4951,22 +4951,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0978848729798846</v>
+        <v>0.09868582796981032</v>
       </c>
       <c r="C42">
-        <v>204.6247324923637</v>
+        <v>198.900050428885</v>
       </c>
       <c r="D42">
-        <v>270.1727324923638</v>
+        <v>267.714250428885</v>
       </c>
       <c r="E42">
-        <v>128.928</v>
+        <v>132.1942</v>
       </c>
       <c r="F42">
-        <v>130.648</v>
+        <v>133.9142</v>
       </c>
       <c r="G42">
         <v>65.09999999999999</v>
@@ -4987,45 +4987,45 @@
         <v>33.296</v>
       </c>
       <c r="M42">
-        <v>7.2248344</v>
+        <v>7.740240760000002</v>
       </c>
       <c r="N42">
-        <v>26.0711656</v>
+        <v>25.55575924</v>
       </c>
       <c r="O42">
-        <v>3.91067484</v>
+        <v>3.833363885999999</v>
       </c>
       <c r="P42">
-        <v>22.16049076</v>
+        <v>21.722395354</v>
       </c>
       <c r="Q42">
-        <v>22.76449076</v>
+        <v>22.326395354</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1318047882998077</v>
+        <v>0.1331229287623904</v>
       </c>
       <c r="T42">
-        <v>1.12093070552405</v>
+        <v>1.138110494555702</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.608548536420434</v>
+        <v>4.301674977872393</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5033,22 +5033,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09868582796981032</v>
+        <v>0.09863678295973605</v>
       </c>
       <c r="C43">
-        <v>198.900050428885</v>
+        <v>195.78310436457</v>
       </c>
       <c r="D43">
-        <v>267.714250428885</v>
+        <v>267.86350436457</v>
       </c>
       <c r="E43">
-        <v>132.1942</v>
+        <v>135.4604</v>
       </c>
       <c r="F43">
-        <v>133.9142</v>
+        <v>137.1804</v>
       </c>
       <c r="G43">
         <v>65.09999999999999</v>
@@ -5069,28 +5069,28 @@
         <v>33.296</v>
       </c>
       <c r="M43">
-        <v>7.740240760000002</v>
+        <v>7.929027120000002</v>
       </c>
       <c r="N43">
-        <v>25.55575924</v>
+        <v>25.36697288</v>
       </c>
       <c r="O43">
-        <v>3.833363885999999</v>
+        <v>3.805045932</v>
       </c>
       <c r="P43">
-        <v>21.722395354</v>
+        <v>21.561926948</v>
       </c>
       <c r="Q43">
-        <v>22.326395354</v>
+        <v>22.165926948</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1331229287623904</v>
+        <v>0.1344865223443725</v>
       </c>
       <c r="T43">
-        <v>1.138110494555702</v>
+        <v>1.155882690105687</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.301674977872393</v>
+        <v>4.199254145065908</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5115,22 +5115,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09863678295973605</v>
+        <v>0.09858773794966177</v>
       </c>
       <c r="C44">
-        <v>195.78310436457</v>
+        <v>192.666324814841</v>
       </c>
       <c r="D44">
-        <v>267.86350436457</v>
+        <v>268.012924814841</v>
       </c>
       <c r="E44">
-        <v>135.4604</v>
+        <v>138.7266</v>
       </c>
       <c r="F44">
-        <v>137.1804</v>
+        <v>140.4466</v>
       </c>
       <c r="G44">
         <v>65.09999999999999</v>
@@ -5151,28 +5151,28 @@
         <v>33.296</v>
       </c>
       <c r="M44">
-        <v>7.92902712</v>
+        <v>8.117813480000001</v>
       </c>
       <c r="N44">
-        <v>25.36697288</v>
+        <v>25.17818652</v>
       </c>
       <c r="O44">
-        <v>3.805045932</v>
+        <v>3.776727977999999</v>
       </c>
       <c r="P44">
-        <v>21.561926948</v>
+        <v>21.401458542</v>
       </c>
       <c r="Q44">
-        <v>22.165926948</v>
+        <v>22.005458542</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1344865223443725</v>
+        <v>0.1358979613151961</v>
       </c>
       <c r="T44">
-        <v>1.155882690105687</v>
+        <v>1.174278471464444</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.199254145065908</v>
+        <v>4.101597071924839</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5197,22 +5197,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09858773794966177</v>
+        <v>0.09853869293958747</v>
       </c>
       <c r="C45">
-        <v>192.666324814841</v>
+        <v>189.5497120585106</v>
       </c>
       <c r="D45">
-        <v>268.012924814841</v>
+        <v>268.1625120585107</v>
       </c>
       <c r="E45">
-        <v>138.7266</v>
+        <v>141.9928</v>
       </c>
       <c r="F45">
-        <v>140.4466</v>
+        <v>143.7128</v>
       </c>
       <c r="G45">
         <v>65.09999999999999</v>
@@ -5233,28 +5233,28 @@
         <v>33.296</v>
       </c>
       <c r="M45">
-        <v>8.117813480000001</v>
+        <v>8.306599840000002</v>
       </c>
       <c r="N45">
-        <v>25.17818652</v>
+        <v>24.98940016</v>
       </c>
       <c r="O45">
-        <v>3.776727977999999</v>
+        <v>3.748410023999999</v>
       </c>
       <c r="P45">
-        <v>21.401458542</v>
+        <v>21.240990136</v>
       </c>
       <c r="Q45">
-        <v>22.005458542</v>
+        <v>21.844990136</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1358979613151961</v>
+        <v>0.1373598088206919</v>
       </c>
       <c r="T45">
-        <v>1.174278471464444</v>
+        <v>1.193331245014585</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.101597071924839</v>
+        <v>4.00837895665382</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09853869293958747</v>
+        <v>0.09982839792951319</v>
       </c>
       <c r="C46">
-        <v>189.5497120585106</v>
+        <v>182.4046470552978</v>
       </c>
       <c r="D46">
-        <v>268.1625120585107</v>
+        <v>264.2836470552979</v>
       </c>
       <c r="E46">
-        <v>141.9928</v>
+        <v>145.259</v>
       </c>
       <c r="F46">
-        <v>143.7128</v>
+        <v>146.979</v>
       </c>
       <c r="G46">
         <v>65.09999999999999</v>
@@ -5315,45 +5315,45 @@
         <v>33.296</v>
       </c>
       <c r="M46">
-        <v>8.306599840000002</v>
+        <v>9.009812700000001</v>
       </c>
       <c r="N46">
-        <v>24.98940016</v>
+        <v>24.2861873</v>
       </c>
       <c r="O46">
-        <v>3.748410023999999</v>
+        <v>3.642928094999999</v>
       </c>
       <c r="P46">
-        <v>21.240990136</v>
+        <v>20.643259205</v>
       </c>
       <c r="Q46">
-        <v>21.844990136</v>
+        <v>21.247259205</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1373598088206919</v>
+        <v>0.1388748144172967</v>
       </c>
       <c r="T46">
-        <v>1.193331245014585</v>
+        <v>1.213076846693821</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.15</v>
       </c>
       <c r="W46">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.00837895665382</v>
+        <v>3.695526323205364</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5361,22 +5361,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09982839792951319</v>
+        <v>0.09980910291943891</v>
       </c>
       <c r="C47">
-        <v>182.4046470552978</v>
+        <v>179.1956509387263</v>
       </c>
       <c r="D47">
-        <v>264.2836470552979</v>
+        <v>264.3408509387262</v>
       </c>
       <c r="E47">
-        <v>145.259</v>
+        <v>148.5252</v>
       </c>
       <c r="F47">
-        <v>146.979</v>
+        <v>150.2452</v>
       </c>
       <c r="G47">
         <v>65.09999999999999</v>
@@ -5397,28 +5397,28 @@
         <v>33.296</v>
       </c>
       <c r="M47">
-        <v>9.009812700000001</v>
+        <v>9.21003076</v>
       </c>
       <c r="N47">
-        <v>24.2861873</v>
+        <v>24.08596924</v>
       </c>
       <c r="O47">
-        <v>3.642928094999999</v>
+        <v>3.612895385999999</v>
       </c>
       <c r="P47">
-        <v>20.643259205</v>
+        <v>20.473073854</v>
       </c>
       <c r="Q47">
-        <v>21.247259205</v>
+        <v>21.077073854</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1388748144172967</v>
+        <v>0.1404459313322943</v>
       </c>
       <c r="T47">
-        <v>1.213076846693821</v>
+        <v>1.233553766953771</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.695526323205364</v>
+        <v>3.61518879444003</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5443,22 +5443,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09980910291943891</v>
+        <v>0.09978980790936462</v>
       </c>
       <c r="C48">
-        <v>179.1956509387263</v>
+        <v>175.9866795909419</v>
       </c>
       <c r="D48">
-        <v>264.3408509387262</v>
+        <v>264.3980795909419</v>
       </c>
       <c r="E48">
-        <v>148.5252</v>
+        <v>151.7914</v>
       </c>
       <c r="F48">
-        <v>150.2452</v>
+        <v>153.5114</v>
       </c>
       <c r="G48">
         <v>65.09999999999999</v>
@@ -5479,28 +5479,28 @@
         <v>33.296</v>
       </c>
       <c r="M48">
-        <v>9.21003076</v>
+        <v>9.410248820000001</v>
       </c>
       <c r="N48">
-        <v>24.08596924</v>
+        <v>23.88575118</v>
       </c>
       <c r="O48">
-        <v>3.612895385999999</v>
+        <v>3.582862677</v>
       </c>
       <c r="P48">
-        <v>20.473073854</v>
+        <v>20.302888503</v>
       </c>
       <c r="Q48">
-        <v>21.077073854</v>
+        <v>20.906888503</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1404459313322943</v>
+        <v>0.1420763356780465</v>
       </c>
       <c r="T48">
-        <v>1.233553766953771</v>
+        <v>1.254803401185794</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.61518879444003</v>
+        <v>3.53826988392003</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5525,22 +5525,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09978980790936462</v>
+        <v>0.1009129128992903</v>
       </c>
       <c r="C49">
-        <v>175.9866795909419</v>
+        <v>169.4301130339589</v>
       </c>
       <c r="D49">
-        <v>264.3980795909419</v>
+        <v>261.1077130339589</v>
       </c>
       <c r="E49">
-        <v>151.7914</v>
+        <v>155.0576</v>
       </c>
       <c r="F49">
-        <v>153.5114</v>
+        <v>156.7776</v>
       </c>
       <c r="G49">
         <v>65.09999999999999</v>
@@ -5561,45 +5561,45 @@
         <v>33.296</v>
       </c>
       <c r="M49">
-        <v>9.410248820000001</v>
+        <v>10.04944416</v>
       </c>
       <c r="N49">
-        <v>23.88575118</v>
+        <v>23.24655584</v>
       </c>
       <c r="O49">
-        <v>3.582862677</v>
+        <v>3.486983376</v>
       </c>
       <c r="P49">
-        <v>20.302888503</v>
+        <v>19.759572464</v>
       </c>
       <c r="Q49">
-        <v>20.906888503</v>
+        <v>20.363572464</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1420763356780465</v>
+        <v>0.1437694478832506</v>
       </c>
       <c r="T49">
-        <v>1.254803401185794</v>
+        <v>1.276870329042125</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.15</v>
       </c>
       <c r="W49">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.53826988392003</v>
+        <v>3.313218071555511</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5607,22 +5607,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1009129128992903</v>
+        <v>0.1009174178892161</v>
       </c>
       <c r="C50">
-        <v>169.4301130339589</v>
+        <v>166.150879641419</v>
       </c>
       <c r="D50">
-        <v>261.1077130339589</v>
+        <v>261.094679641419</v>
       </c>
       <c r="E50">
-        <v>155.0576</v>
+        <v>158.3238</v>
       </c>
       <c r="F50">
-        <v>156.7776</v>
+        <v>160.0438</v>
       </c>
       <c r="G50">
         <v>65.09999999999999</v>
@@ -5643,28 +5643,28 @@
         <v>33.296</v>
       </c>
       <c r="M50">
-        <v>10.04944416</v>
+        <v>10.25880758</v>
       </c>
       <c r="N50">
-        <v>23.24655584</v>
+        <v>23.03719242</v>
       </c>
       <c r="O50">
-        <v>3.486983376</v>
+        <v>3.455578863</v>
       </c>
       <c r="P50">
-        <v>19.759572464</v>
+        <v>19.581613557</v>
       </c>
       <c r="Q50">
-        <v>20.363572464</v>
+        <v>20.185613557</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1437694478832506</v>
+        <v>0.1455289566455217</v>
       </c>
       <c r="T50">
-        <v>1.276870329042125</v>
+        <v>1.299802626618313</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.313218071555511</v>
+        <v>3.245601376217644</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5689,22 +5689,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1009174178892161</v>
+        <v>0.1009219228791418</v>
       </c>
       <c r="C51">
-        <v>166.150879641419</v>
+        <v>162.8716475499578</v>
       </c>
       <c r="D51">
-        <v>261.094679641419</v>
+        <v>261.0816475499578</v>
       </c>
       <c r="E51">
-        <v>158.3238</v>
+        <v>161.59</v>
       </c>
       <c r="F51">
-        <v>160.0438</v>
+        <v>163.31</v>
       </c>
       <c r="G51">
         <v>65.09999999999999</v>
@@ -5725,28 +5725,28 @@
         <v>33.296</v>
       </c>
       <c r="M51">
-        <v>10.25880758</v>
+        <v>10.468171</v>
       </c>
       <c r="N51">
-        <v>23.03719242</v>
+        <v>22.827829</v>
       </c>
       <c r="O51">
-        <v>3.455578863</v>
+        <v>3.424174349999999</v>
       </c>
       <c r="P51">
-        <v>19.581613557</v>
+        <v>19.40365465</v>
       </c>
       <c r="Q51">
-        <v>20.185613557</v>
+        <v>20.00765465</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1455289566455217</v>
+        <v>0.1473588457582835</v>
       </c>
       <c r="T51">
-        <v>1.299802626618313</v>
+        <v>1.323652216097548</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.245601376217644</v>
+        <v>3.180689348693291</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5771,22 +5771,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1009219228791418</v>
+        <v>0.1009264278690675</v>
       </c>
       <c r="C52">
-        <v>162.8716475499578</v>
+        <v>159.5924167593804</v>
       </c>
       <c r="D52">
-        <v>261.0816475499578</v>
+        <v>261.0686167593804</v>
       </c>
       <c r="E52">
-        <v>161.59</v>
+        <v>164.8562</v>
       </c>
       <c r="F52">
-        <v>163.31</v>
+        <v>166.5762</v>
       </c>
       <c r="G52">
         <v>65.09999999999999</v>
@@ -5807,28 +5807,28 @@
         <v>33.296</v>
       </c>
       <c r="M52">
-        <v>10.468171</v>
+        <v>10.67753442</v>
       </c>
       <c r="N52">
-        <v>22.827829</v>
+        <v>22.61846558</v>
       </c>
       <c r="O52">
-        <v>3.424174349999999</v>
+        <v>3.392769837</v>
       </c>
       <c r="P52">
-        <v>19.40365465</v>
+        <v>19.225695743</v>
       </c>
       <c r="Q52">
-        <v>20.00765465</v>
+        <v>19.829695743</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1473588457582835</v>
+        <v>0.1492634242225867</v>
       </c>
       <c r="T52">
-        <v>1.323652216097548</v>
+        <v>1.348475258208589</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.180689348693291</v>
+        <v>3.118322890875775</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5853,22 +5853,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1009264278690675</v>
+        <v>0.1009309328589932</v>
       </c>
       <c r="C53">
-        <v>159.5924167593804</v>
+        <v>156.3131872694921</v>
       </c>
       <c r="D53">
-        <v>261.0686167593804</v>
+        <v>261.0555872694922</v>
       </c>
       <c r="E53">
-        <v>164.8562</v>
+        <v>168.1224</v>
       </c>
       <c r="F53">
-        <v>166.5762</v>
+        <v>169.8424</v>
       </c>
       <c r="G53">
         <v>65.09999999999999</v>
@@ -5889,28 +5889,28 @@
         <v>33.296</v>
       </c>
       <c r="M53">
-        <v>10.67753442</v>
+        <v>10.88689784</v>
       </c>
       <c r="N53">
-        <v>22.61846558</v>
+        <v>22.40910216</v>
       </c>
       <c r="O53">
-        <v>3.392769837</v>
+        <v>3.361365323999999</v>
       </c>
       <c r="P53">
-        <v>19.225695743</v>
+        <v>19.047736836</v>
       </c>
       <c r="Q53">
-        <v>19.829695743</v>
+        <v>19.651736836</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1492634242225867</v>
+        <v>0.1512473601229025</v>
       </c>
       <c r="T53">
-        <v>1.348475258208589</v>
+        <v>1.374332593740923</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.118322890875775</v>
+        <v>3.058355142974318</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5935,22 +5935,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1009309328589932</v>
+        <v>0.1009354378489189</v>
       </c>
       <c r="C54">
-        <v>156.3131872694921</v>
+        <v>153.0339590800983</v>
       </c>
       <c r="D54">
-        <v>261.0555872694922</v>
+        <v>261.0425590800983</v>
       </c>
       <c r="E54">
-        <v>168.1224</v>
+        <v>171.3886</v>
       </c>
       <c r="F54">
-        <v>169.8424</v>
+        <v>173.1086</v>
       </c>
       <c r="G54">
         <v>65.09999999999999</v>
@@ -5971,28 +5971,28 @@
         <v>33.296</v>
       </c>
       <c r="M54">
-        <v>10.88689784</v>
+        <v>11.09626126</v>
       </c>
       <c r="N54">
-        <v>22.40910216</v>
+        <v>22.19973874</v>
       </c>
       <c r="O54">
-        <v>3.361365323999999</v>
+        <v>3.329960810999999</v>
       </c>
       <c r="P54">
-        <v>19.047736836</v>
+        <v>18.869777929</v>
       </c>
       <c r="Q54">
-        <v>19.651736836</v>
+        <v>19.473777929</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1512473601229025</v>
+        <v>0.153315718827487</v>
       </c>
       <c r="T54">
-        <v>1.374332593740923</v>
+        <v>1.401290241423568</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.058355142974318</v>
+        <v>3.000650328955935</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6017,22 +6017,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1009354378489189</v>
+        <v>0.1045201428388446</v>
       </c>
       <c r="C55">
-        <v>153.0339590800983</v>
+        <v>139.7974332220977</v>
       </c>
       <c r="D55">
-        <v>261.0425590800983</v>
+        <v>251.0722332220977</v>
       </c>
       <c r="E55">
-        <v>171.3886</v>
+        <v>174.6548</v>
       </c>
       <c r="F55">
-        <v>173.1086</v>
+        <v>176.3748</v>
       </c>
       <c r="G55">
         <v>65.09999999999999</v>
@@ -6053,45 +6053,45 @@
         <v>33.296</v>
       </c>
       <c r="M55">
-        <v>11.09626126</v>
+        <v>12.68134812</v>
       </c>
       <c r="N55">
-        <v>22.19973874</v>
+        <v>20.61465188</v>
       </c>
       <c r="O55">
-        <v>3.329960810999999</v>
+        <v>3.092197782</v>
       </c>
       <c r="P55">
-        <v>18.869777929</v>
+        <v>17.522454098</v>
       </c>
       <c r="Q55">
-        <v>19.473777929</v>
+        <v>18.126454098</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.153315718827487</v>
+        <v>0.1554740061714014</v>
       </c>
       <c r="T55">
-        <v>1.401290241423568</v>
+        <v>1.429419960744591</v>
       </c>
       <c r="U55">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V55">
         <v>0.15</v>
       </c>
       <c r="W55">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.000650328955935</v>
+        <v>2.625588358976458</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6099,22 +6099,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1045201428388446</v>
+        <v>0.1045909478287703</v>
       </c>
       <c r="C56">
-        <v>139.7974332220977</v>
+        <v>136.3419641507386</v>
       </c>
       <c r="D56">
-        <v>251.0722332220977</v>
+        <v>250.8829641507387</v>
       </c>
       <c r="E56">
-        <v>174.6548</v>
+        <v>177.921</v>
       </c>
       <c r="F56">
-        <v>176.3748</v>
+        <v>179.641</v>
       </c>
       <c r="G56">
         <v>65.09999999999999</v>
@@ -6135,28 +6135,28 @@
         <v>33.296</v>
       </c>
       <c r="M56">
-        <v>12.68134812</v>
+        <v>12.9161879</v>
       </c>
       <c r="N56">
-        <v>20.61465188</v>
+        <v>20.3798121</v>
       </c>
       <c r="O56">
-        <v>3.092197782</v>
+        <v>3.056971814999999</v>
       </c>
       <c r="P56">
-        <v>17.522454098</v>
+        <v>17.32284028499999</v>
       </c>
       <c r="Q56">
-        <v>18.126454098</v>
+        <v>17.92684028499999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1554740061714014</v>
+        <v>0.1577282173972675</v>
       </c>
       <c r="T56">
-        <v>1.429419960744591</v>
+        <v>1.458799889813214</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.625588358976458</v>
+        <v>2.57785038881325</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6181,22 +6181,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1045909478287703</v>
+        <v>0.1046617528186961</v>
       </c>
       <c r="C57">
-        <v>136.3419641507386</v>
+        <v>132.8867802227942</v>
       </c>
       <c r="D57">
-        <v>250.8829641507387</v>
+        <v>250.6939802227942</v>
       </c>
       <c r="E57">
-        <v>177.921</v>
+        <v>181.1872</v>
       </c>
       <c r="F57">
-        <v>179.641</v>
+        <v>182.9072</v>
       </c>
       <c r="G57">
         <v>65.09999999999999</v>
@@ -6217,28 +6217,28 @@
         <v>33.296</v>
       </c>
       <c r="M57">
-        <v>12.9161879</v>
+        <v>13.15102768</v>
       </c>
       <c r="N57">
-        <v>20.3798121</v>
+        <v>20.14497232</v>
       </c>
       <c r="O57">
-        <v>3.056971814999999</v>
+        <v>3.021745848</v>
       </c>
       <c r="P57">
-        <v>17.32284028499999</v>
+        <v>17.123226472</v>
       </c>
       <c r="Q57">
-        <v>17.92684028499999</v>
+        <v>17.727226472</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1577282173972675</v>
+        <v>0.1600848927697638</v>
       </c>
       <c r="T57">
-        <v>1.458799889813214</v>
+        <v>1.489515270203138</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.57785038881325</v>
+        <v>2.53181734615587</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6263,22 +6263,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1046617528186961</v>
+        <v>0.1066221078086218</v>
       </c>
       <c r="C58">
-        <v>132.8867802227942</v>
+        <v>124.4989984839995</v>
       </c>
       <c r="D58">
-        <v>250.6939802227942</v>
+        <v>245.5723984839995</v>
       </c>
       <c r="E58">
-        <v>181.1872</v>
+        <v>184.4534</v>
       </c>
       <c r="F58">
-        <v>182.9072</v>
+        <v>186.1734</v>
       </c>
       <c r="G58">
         <v>65.09999999999999</v>
@@ -6299,45 +6299,45 @@
         <v>33.296</v>
       </c>
       <c r="M58">
-        <v>13.15102768</v>
+        <v>14.11194372</v>
       </c>
       <c r="N58">
-        <v>20.14497232</v>
+        <v>19.18405628</v>
       </c>
       <c r="O58">
-        <v>3.021745848</v>
+        <v>2.877608441999999</v>
       </c>
       <c r="P58">
-        <v>17.123226472</v>
+        <v>16.306447838</v>
       </c>
       <c r="Q58">
-        <v>17.727226472</v>
+        <v>16.910447838</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1600848927697638</v>
+        <v>0.1625511809502832</v>
       </c>
       <c r="T58">
-        <v>1.489515270203138</v>
+        <v>1.521659272936779</v>
       </c>
       <c r="U58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.15</v>
       </c>
       <c r="W58">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.53181734615587</v>
+        <v>2.359419840430032</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1066221078086218</v>
+        <v>0.1067260627985475</v>
       </c>
       <c r="C59">
-        <v>124.4989984839995</v>
+        <v>120.9670442867429</v>
       </c>
       <c r="D59">
-        <v>245.5723984839995</v>
+        <v>245.306644286743</v>
       </c>
       <c r="E59">
-        <v>184.4534</v>
+        <v>187.7196</v>
       </c>
       <c r="F59">
-        <v>186.1734</v>
+        <v>189.4396</v>
       </c>
       <c r="G59">
         <v>65.09999999999999</v>
@@ -6381,28 +6381,28 @@
         <v>33.296</v>
       </c>
       <c r="M59">
-        <v>14.11194372</v>
+        <v>14.35952168</v>
       </c>
       <c r="N59">
-        <v>19.18405628</v>
+        <v>18.93647832</v>
       </c>
       <c r="O59">
-        <v>2.877608441999999</v>
+        <v>2.840471748</v>
       </c>
       <c r="P59">
-        <v>16.306447838</v>
+        <v>16.096006572</v>
       </c>
       <c r="Q59">
-        <v>16.910447838</v>
+        <v>16.700006572</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1625511809502832</v>
+        <v>0.1651349114251131</v>
       </c>
       <c r="T59">
-        <v>1.521659272936779</v>
+        <v>1.555333942467261</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.359419840430032</v>
+        <v>2.318740188008825</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6427,22 +6427,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1067260627985475</v>
+        <v>0.1068300177884732</v>
       </c>
       <c r="C60">
-        <v>120.9670442867429</v>
+        <v>117.4356646568803</v>
       </c>
       <c r="D60">
-        <v>245.3066442867429</v>
+        <v>245.0414646568804</v>
       </c>
       <c r="E60">
-        <v>187.7196</v>
+        <v>190.9858</v>
       </c>
       <c r="F60">
-        <v>189.4396</v>
+        <v>192.7058</v>
       </c>
       <c r="G60">
         <v>65.09999999999999</v>
@@ -6463,28 +6463,28 @@
         <v>33.296</v>
       </c>
       <c r="M60">
-        <v>14.35952168</v>
+        <v>14.60709964</v>
       </c>
       <c r="N60">
-        <v>18.93647832</v>
+        <v>18.68890036</v>
       </c>
       <c r="O60">
-        <v>2.840471748</v>
+        <v>2.803335054</v>
       </c>
       <c r="P60">
-        <v>16.096006572</v>
+        <v>15.885565306</v>
       </c>
       <c r="Q60">
-        <v>16.700006572</v>
+        <v>16.489565306</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1651349114251131</v>
+        <v>0.1678446775328615</v>
       </c>
       <c r="T60">
-        <v>1.55533394246726</v>
+        <v>1.590651278804106</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.318740188008825</v>
+        <v>2.279439506856133</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6509,22 +6509,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1068300177884732</v>
+        <v>0.1069339727783989</v>
       </c>
       <c r="C61">
-        <v>117.4356646568803</v>
+        <v>113.9048577330796</v>
       </c>
       <c r="D61">
-        <v>245.0414646568804</v>
+        <v>244.7768577330797</v>
       </c>
       <c r="E61">
-        <v>190.9858</v>
+        <v>194.252</v>
       </c>
       <c r="F61">
-        <v>192.7058</v>
+        <v>195.972</v>
       </c>
       <c r="G61">
         <v>65.09999999999999</v>
@@ -6545,28 +6545,28 @@
         <v>33.296</v>
       </c>
       <c r="M61">
-        <v>14.60709964</v>
+        <v>14.8546776</v>
       </c>
       <c r="N61">
-        <v>18.68890036</v>
+        <v>18.4413224</v>
       </c>
       <c r="O61">
-        <v>2.803335054</v>
+        <v>2.766198359999999</v>
       </c>
       <c r="P61">
-        <v>15.885565306</v>
+        <v>15.67512404</v>
       </c>
       <c r="Q61">
-        <v>16.489565306</v>
+        <v>16.27912404</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1678446775328615</v>
+        <v>0.1706899319459973</v>
       </c>
       <c r="T61">
-        <v>1.590651278804106</v>
+        <v>1.627734481957795</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.279439506856133</v>
+        <v>2.241448848408531</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6591,22 +6591,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1069339727783989</v>
+        <v>0.1070379277683246</v>
       </c>
       <c r="C62">
-        <v>113.9048577330796</v>
+        <v>110.3746216620399</v>
       </c>
       <c r="D62">
-        <v>244.7768577330797</v>
+        <v>244.5128216620399</v>
       </c>
       <c r="E62">
-        <v>194.252</v>
+        <v>197.5182</v>
       </c>
       <c r="F62">
-        <v>195.972</v>
+        <v>199.2382</v>
       </c>
       <c r="G62">
         <v>65.09999999999999</v>
@@ -6627,28 +6627,28 @@
         <v>33.296</v>
       </c>
       <c r="M62">
-        <v>14.8546776</v>
+        <v>15.10225556</v>
       </c>
       <c r="N62">
-        <v>18.4413224</v>
+        <v>18.19374444</v>
       </c>
       <c r="O62">
-        <v>2.766198359999999</v>
+        <v>2.729061665999999</v>
       </c>
       <c r="P62">
-        <v>15.67512404</v>
+        <v>15.464682774</v>
       </c>
       <c r="Q62">
-        <v>16.27912404</v>
+        <v>16.068682774</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1706899319459973</v>
+        <v>0.1736810968418581</v>
       </c>
       <c r="T62">
-        <v>1.627734481957795</v>
+        <v>1.666719387837314</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.241448848408531</v>
+        <v>2.204703785319866</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6673,22 +6673,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1070379277683246</v>
+        <v>0.1071418827582504</v>
       </c>
       <c r="C63">
-        <v>110.3746216620399</v>
+        <v>106.8449545984481</v>
       </c>
       <c r="D63">
-        <v>244.5128216620399</v>
+        <v>244.2493545984481</v>
       </c>
       <c r="E63">
-        <v>197.5182</v>
+        <v>200.7844</v>
       </c>
       <c r="F63">
-        <v>199.2382</v>
+        <v>202.5044</v>
       </c>
       <c r="G63">
         <v>65.09999999999999</v>
@@ -6709,28 +6709,28 @@
         <v>33.296</v>
       </c>
       <c r="M63">
-        <v>15.10225556</v>
+        <v>15.34983352</v>
       </c>
       <c r="N63">
-        <v>18.19374444</v>
+        <v>17.94616648</v>
       </c>
       <c r="O63">
-        <v>2.729061665999999</v>
+        <v>2.691924971999999</v>
       </c>
       <c r="P63">
-        <v>15.464682774</v>
+        <v>15.254241508</v>
       </c>
       <c r="Q63">
-        <v>16.068682774</v>
+        <v>15.858241508</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1736810968418581</v>
+        <v>0.1768296914690799</v>
       </c>
       <c r="T63">
-        <v>1.666719387837314</v>
+        <v>1.707756130868387</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.204703785319866</v>
+        <v>2.169144046846965</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6755,22 +6755,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1071418827582504</v>
+        <v>0.1072458377481761</v>
       </c>
       <c r="C64">
-        <v>106.8449545984481</v>
+        <v>103.315854704936</v>
       </c>
       <c r="D64">
-        <v>244.2493545984481</v>
+        <v>243.9864547049361</v>
       </c>
       <c r="E64">
-        <v>200.7844</v>
+        <v>204.0506</v>
       </c>
       <c r="F64">
-        <v>202.5044</v>
+        <v>205.7706</v>
       </c>
       <c r="G64">
         <v>65.09999999999999</v>
@@ -6791,28 +6791,28 @@
         <v>33.296</v>
       </c>
       <c r="M64">
-        <v>15.34983352</v>
+        <v>15.59741148</v>
       </c>
       <c r="N64">
-        <v>17.94616648</v>
+        <v>17.69858852</v>
       </c>
       <c r="O64">
-        <v>2.691924971999999</v>
+        <v>2.654788277999999</v>
       </c>
       <c r="P64">
-        <v>15.254241508</v>
+        <v>15.043800242</v>
       </c>
       <c r="Q64">
-        <v>15.858241508</v>
+        <v>15.647800242</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1768296914690799</v>
+        <v>0.1801484804004759</v>
       </c>
       <c r="T64">
-        <v>1.707756130868387</v>
+        <v>1.751011076225463</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.169144046846965</v>
+        <v>2.134713188960506</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6837,22 +6837,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1072458377481761</v>
+        <v>0.1073497927381018</v>
       </c>
       <c r="C65">
-        <v>103.315854704936</v>
+        <v>99.78732015203772</v>
       </c>
       <c r="D65">
-        <v>243.9864547049361</v>
+        <v>243.7241201520378</v>
       </c>
       <c r="E65">
-        <v>204.0506</v>
+        <v>207.3168</v>
       </c>
       <c r="F65">
-        <v>205.7706</v>
+        <v>209.0368</v>
       </c>
       <c r="G65">
         <v>65.09999999999999</v>
@@ -6873,28 +6873,28 @@
         <v>33.296</v>
       </c>
       <c r="M65">
-        <v>15.59741148</v>
+        <v>15.84498944</v>
       </c>
       <c r="N65">
-        <v>17.69858852</v>
+        <v>17.45101056</v>
       </c>
       <c r="O65">
-        <v>2.654788277999999</v>
+        <v>2.617651584</v>
       </c>
       <c r="P65">
-        <v>15.043800242</v>
+        <v>14.833358976</v>
       </c>
       <c r="Q65">
-        <v>15.647800242</v>
+        <v>15.437358976</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1801484804004759</v>
+        <v>0.1836516464947272</v>
       </c>
       <c r="T65">
-        <v>1.751011076225463</v>
+        <v>1.796669074102377</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.134713188960506</v>
+        <v>2.101358295382997</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6919,22 +6919,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1073497927381018</v>
+        <v>0.1074537477280275</v>
       </c>
       <c r="C66">
-        <v>99.78732015203772</v>
+        <v>96.25934911814682</v>
       </c>
       <c r="D66">
-        <v>243.7241201520378</v>
+        <v>243.4623491181468</v>
       </c>
       <c r="E66">
-        <v>207.3168</v>
+        <v>210.583</v>
       </c>
       <c r="F66">
-        <v>209.0368</v>
+        <v>212.303</v>
       </c>
       <c r="G66">
         <v>65.09999999999999</v>
@@ -6955,28 +6955,28 @@
         <v>33.296</v>
       </c>
       <c r="M66">
-        <v>15.84498944</v>
+        <v>16.0925674</v>
       </c>
       <c r="N66">
-        <v>17.45101056</v>
+        <v>17.2034326</v>
       </c>
       <c r="O66">
-        <v>2.617651584</v>
+        <v>2.58051489</v>
       </c>
       <c r="P66">
-        <v>14.833358976</v>
+        <v>14.62291771</v>
       </c>
       <c r="Q66">
-        <v>15.437358976</v>
+        <v>15.22691771</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1836516464947272</v>
+        <v>0.18735499350865</v>
       </c>
       <c r="T66">
-        <v>1.796669074102377</v>
+        <v>1.844936100429401</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.101358295382997</v>
+        <v>2.069029706223259</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7001,22 +7001,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1074537477280275</v>
+        <v>0.1075577027179532</v>
       </c>
       <c r="C67">
-        <v>96.25934911814682</v>
+        <v>92.73193978947461</v>
       </c>
       <c r="D67">
-        <v>243.4623491181468</v>
+        <v>243.2011397894746</v>
       </c>
       <c r="E67">
-        <v>210.583</v>
+        <v>213.8492</v>
       </c>
       <c r="F67">
-        <v>212.303</v>
+        <v>215.5692</v>
       </c>
       <c r="G67">
         <v>65.09999999999999</v>
@@ -7037,28 +7037,28 @@
         <v>33.296</v>
       </c>
       <c r="M67">
-        <v>16.0925674</v>
+        <v>16.34014536</v>
       </c>
       <c r="N67">
-        <v>17.2034326</v>
+        <v>16.95585463999999</v>
       </c>
       <c r="O67">
-        <v>2.58051489</v>
+        <v>2.543378195999999</v>
       </c>
       <c r="P67">
-        <v>14.62291771</v>
+        <v>14.412476444</v>
       </c>
       <c r="Q67">
-        <v>15.22691771</v>
+        <v>15.01647644399999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.18735499350865</v>
+        <v>0.1912761844645683</v>
       </c>
       <c r="T67">
-        <v>1.844936100429401</v>
+        <v>1.896042363599191</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.069029706223259</v>
+        <v>2.037680771280482</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7083,22 +7083,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1075577027179532</v>
+        <v>0.1076616577078789</v>
       </c>
       <c r="C68">
-        <v>92.73193978947461</v>
+        <v>89.20509036000809</v>
       </c>
       <c r="D68">
-        <v>243.2011397894746</v>
+        <v>242.9404903600081</v>
       </c>
       <c r="E68">
-        <v>213.8492</v>
+        <v>217.1154</v>
       </c>
       <c r="F68">
-        <v>215.5692</v>
+        <v>218.8354</v>
       </c>
       <c r="G68">
         <v>65.09999999999999</v>
@@ -7119,28 +7119,28 @@
         <v>33.296</v>
       </c>
       <c r="M68">
-        <v>16.34014536</v>
+        <v>16.58772332</v>
       </c>
       <c r="N68">
-        <v>16.95585463999999</v>
+        <v>16.70827668</v>
       </c>
       <c r="O68">
-        <v>2.543378195999999</v>
+        <v>2.506241502</v>
       </c>
       <c r="P68">
-        <v>14.412476444</v>
+        <v>14.202035178</v>
       </c>
       <c r="Q68">
-        <v>15.01647644399999</v>
+        <v>14.806035178</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1912761844645683</v>
+        <v>0.1954350233572089</v>
       </c>
       <c r="T68">
-        <v>1.896042363599191</v>
+        <v>1.950245976051997</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.037680771280482</v>
+        <v>2.007267625440475</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7165,22 +7165,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1076616577078789</v>
+        <v>0.1159732126978047</v>
       </c>
       <c r="C69">
-        <v>89.20509036000809</v>
+        <v>66.7644657371024</v>
       </c>
       <c r="D69">
-        <v>242.9404903600081</v>
+        <v>223.7660657371024</v>
       </c>
       <c r="E69">
-        <v>217.1154</v>
+        <v>220.3816</v>
       </c>
       <c r="F69">
-        <v>218.8354</v>
+        <v>222.1016</v>
       </c>
       <c r="G69">
         <v>65.09999999999999</v>
@@ -7201,45 +7201,45 @@
         <v>33.296</v>
       </c>
       <c r="M69">
-        <v>16.58772332</v>
+        <v>19.989144</v>
       </c>
       <c r="N69">
-        <v>16.70827668</v>
+        <v>13.306856</v>
       </c>
       <c r="O69">
-        <v>2.506241502</v>
+        <v>1.9960284</v>
       </c>
       <c r="P69">
-        <v>14.202035178</v>
+        <v>11.3108276</v>
       </c>
       <c r="Q69">
-        <v>14.806035178</v>
+        <v>11.9148276</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1954350233572089</v>
+        <v>0.1998537896806396</v>
       </c>
       <c r="T69">
-        <v>1.950245976051997</v>
+        <v>2.007837314283105</v>
       </c>
       <c r="U69">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V69">
         <v>0.15</v>
       </c>
       <c r="W69">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.007267625440475</v>
+        <v>1.665704144209477</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7247,22 +7247,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1159732126978047</v>
+        <v>0.1161978676877304</v>
       </c>
       <c r="C70">
-        <v>66.7644657371024</v>
+        <v>63.02191707780608</v>
       </c>
       <c r="D70">
-        <v>223.7660657371024</v>
+        <v>223.2897170778061</v>
       </c>
       <c r="E70">
-        <v>220.3816</v>
+        <v>223.6478</v>
       </c>
       <c r="F70">
-        <v>222.1016</v>
+        <v>225.3678</v>
       </c>
       <c r="G70">
         <v>65.09999999999999</v>
@@ -7283,28 +7283,28 @@
         <v>33.296</v>
       </c>
       <c r="M70">
-        <v>19.989144</v>
+        <v>20.283102</v>
       </c>
       <c r="N70">
-        <v>13.306856</v>
+        <v>13.012898</v>
       </c>
       <c r="O70">
-        <v>1.9960284</v>
+        <v>1.9519347</v>
       </c>
       <c r="P70">
-        <v>11.3108276</v>
+        <v>11.0609633</v>
       </c>
       <c r="Q70">
-        <v>11.9148276</v>
+        <v>11.6649633</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1998537896806396</v>
+        <v>0.2045576377023561</v>
       </c>
       <c r="T70">
-        <v>2.007837314283105</v>
+        <v>2.069144222722671</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.665704144209477</v>
+        <v>1.641563504438325</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7329,22 +7329,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1161978676877304</v>
+        <v>0.1164225226776561</v>
       </c>
       <c r="C71">
-        <v>63.02191707780608</v>
+        <v>59.28139219305592</v>
       </c>
       <c r="D71">
-        <v>223.2897170778061</v>
+        <v>222.815392193056</v>
       </c>
       <c r="E71">
-        <v>223.6478</v>
+        <v>226.914</v>
       </c>
       <c r="F71">
-        <v>225.3678</v>
+        <v>228.634</v>
       </c>
       <c r="G71">
         <v>65.09999999999999</v>
@@ -7365,28 +7365,28 @@
         <v>33.296</v>
       </c>
       <c r="M71">
-        <v>20.283102</v>
+        <v>20.57706</v>
       </c>
       <c r="N71">
-        <v>13.012898</v>
+        <v>12.71894</v>
       </c>
       <c r="O71">
-        <v>1.9519347</v>
+        <v>1.907841</v>
       </c>
       <c r="P71">
-        <v>11.0609633</v>
+        <v>10.811099</v>
       </c>
       <c r="Q71">
-        <v>11.6649633</v>
+        <v>11.415099</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2045576377023561</v>
+        <v>0.209575075592187</v>
       </c>
       <c r="T71">
-        <v>2.069144222722671</v>
+        <v>2.134538258391542</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.641563504438325</v>
+        <v>1.618112597232063</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7411,22 +7411,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1164225226776561</v>
+        <v>0.1166471776675818</v>
       </c>
       <c r="C72">
-        <v>59.28139219305592</v>
+        <v>55.54287821313505</v>
       </c>
       <c r="D72">
-        <v>222.815392193056</v>
+        <v>222.3430782131351</v>
       </c>
       <c r="E72">
-        <v>226.914</v>
+        <v>230.1802</v>
       </c>
       <c r="F72">
-        <v>228.634</v>
+        <v>231.9002</v>
       </c>
       <c r="G72">
         <v>65.09999999999999</v>
@@ -7447,28 +7447,28 @@
         <v>33.296</v>
       </c>
       <c r="M72">
-        <v>20.57706</v>
+        <v>20.871018</v>
       </c>
       <c r="N72">
-        <v>12.71894</v>
+        <v>12.424982</v>
       </c>
       <c r="O72">
-        <v>1.907841</v>
+        <v>1.863747299999999</v>
       </c>
       <c r="P72">
-        <v>10.811099</v>
+        <v>10.5612347</v>
       </c>
       <c r="Q72">
-        <v>11.415099</v>
+        <v>11.1652347</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.209575075592187</v>
+        <v>0.2149385436813167</v>
       </c>
       <c r="T72">
-        <v>2.134538258391542</v>
+        <v>2.204442227554817</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.618112597232063</v>
+        <v>1.595322278961189</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7493,22 +7493,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1166471776675818</v>
+        <v>0.1168718326575075</v>
       </c>
       <c r="C73">
-        <v>55.54287821313511</v>
+        <v>51.80636237721828</v>
       </c>
       <c r="D73">
-        <v>222.3430782131351</v>
+        <v>221.8727623772182</v>
       </c>
       <c r="E73">
-        <v>230.1802</v>
+        <v>233.4464</v>
       </c>
       <c r="F73">
-        <v>231.9002</v>
+        <v>235.1664</v>
       </c>
       <c r="G73">
         <v>65.09999999999999</v>
@@ -7529,28 +7529,28 @@
         <v>33.296</v>
       </c>
       <c r="M73">
-        <v>20.871018</v>
+        <v>21.164976</v>
       </c>
       <c r="N73">
-        <v>12.424982</v>
+        <v>12.131024</v>
       </c>
       <c r="O73">
-        <v>1.8637473</v>
+        <v>1.819653600000001</v>
       </c>
       <c r="P73">
-        <v>10.5612347</v>
+        <v>10.3113704</v>
       </c>
       <c r="Q73">
-        <v>11.1652347</v>
+        <v>10.9153704</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2149385436813166</v>
+        <v>0.2206851166339555</v>
       </c>
       <c r="T73">
-        <v>2.204442227554816</v>
+        <v>2.279339337372611</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.595322278961189</v>
+        <v>1.573165025086729</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7575,22 +7575,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1168718326575075</v>
+        <v>0.1170964876474332</v>
       </c>
       <c r="C74">
-        <v>51.80636237721828</v>
+        <v>48.07183203222266</v>
       </c>
       <c r="D74">
-        <v>221.8727623772182</v>
+        <v>221.4044320322226</v>
       </c>
       <c r="E74">
-        <v>233.4464</v>
+        <v>236.7126</v>
       </c>
       <c r="F74">
-        <v>235.1664</v>
+        <v>238.4326</v>
       </c>
       <c r="G74">
         <v>65.09999999999999</v>
@@ -7611,28 +7611,28 @@
         <v>33.296</v>
       </c>
       <c r="M74">
-        <v>21.164976</v>
+        <v>21.458934</v>
       </c>
       <c r="N74">
-        <v>12.131024</v>
+        <v>11.837066</v>
       </c>
       <c r="O74">
-        <v>1.819653600000001</v>
+        <v>1.7755599</v>
       </c>
       <c r="P74">
-        <v>10.3113704</v>
+        <v>10.0615061</v>
       </c>
       <c r="Q74">
-        <v>10.9153704</v>
+        <v>10.6655061</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2206851166339555</v>
+        <v>0.2268573616571601</v>
       </c>
       <c r="T74">
-        <v>2.279339337372611</v>
+        <v>2.359784381250984</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.573165025086729</v>
+        <v>1.551614819263622</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7657,22 +7657,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1170964876474332</v>
+        <v>0.117321142637359</v>
       </c>
       <c r="C75">
-        <v>48.07183203222266</v>
+        <v>44.33927463167339</v>
       </c>
       <c r="D75">
-        <v>221.4044320322226</v>
+        <v>220.9380746316734</v>
       </c>
       <c r="E75">
-        <v>236.7126</v>
+        <v>239.9788</v>
       </c>
       <c r="F75">
-        <v>238.4326</v>
+        <v>241.6988</v>
       </c>
       <c r="G75">
         <v>65.09999999999999</v>
@@ -7693,28 +7693,28 @@
         <v>33.296</v>
       </c>
       <c r="M75">
-        <v>21.458934</v>
+        <v>21.752892</v>
       </c>
       <c r="N75">
-        <v>11.837066</v>
+        <v>11.543108</v>
       </c>
       <c r="O75">
-        <v>1.7755599</v>
+        <v>1.7314662</v>
       </c>
       <c r="P75">
-        <v>10.0615061</v>
+        <v>9.8116418</v>
       </c>
       <c r="Q75">
-        <v>10.6655061</v>
+        <v>10.4156418</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2268573616571601</v>
+        <v>0.2335043947590729</v>
       </c>
       <c r="T75">
-        <v>2.359784381250984</v>
+        <v>2.446417505427692</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.551614819263622</v>
+        <v>1.530647051435736</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7739,22 +7739,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.117321142637359</v>
+        <v>0.1175457976272847</v>
       </c>
       <c r="C76">
-        <v>44.33927463167339</v>
+        <v>40.60867773458304</v>
       </c>
       <c r="D76">
-        <v>220.9380746316734</v>
+        <v>220.473677734583</v>
       </c>
       <c r="E76">
-        <v>239.9788</v>
+        <v>243.245</v>
       </c>
       <c r="F76">
-        <v>241.6988</v>
+        <v>244.965</v>
       </c>
       <c r="G76">
         <v>65.09999999999999</v>
@@ -7775,28 +7775,28 @@
         <v>33.296</v>
       </c>
       <c r="M76">
-        <v>21.752892</v>
+        <v>22.04685</v>
       </c>
       <c r="N76">
-        <v>11.543108</v>
+        <v>11.24915</v>
       </c>
       <c r="O76">
-        <v>1.7314662</v>
+        <v>1.6873725</v>
       </c>
       <c r="P76">
-        <v>9.8116418</v>
+        <v>9.5617775</v>
       </c>
       <c r="Q76">
-        <v>10.4156418</v>
+        <v>10.1657775</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2335043947590729</v>
+        <v>0.2406831905091387</v>
       </c>
       <c r="T76">
-        <v>2.446417505427692</v>
+        <v>2.539981279538538</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.530647051435736</v>
+        <v>1.510238424083259</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7821,22 +7821,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1175457976272847</v>
+        <v>0.156447293820222</v>
       </c>
       <c r="C77">
-        <v>40.60867773458304</v>
+        <v>-21.49038801449083</v>
       </c>
       <c r="D77">
-        <v>220.473677734583</v>
+        <v>161.6408119855092</v>
       </c>
       <c r="E77">
-        <v>243.245</v>
+        <v>246.5112</v>
       </c>
       <c r="F77">
-        <v>244.965</v>
+        <v>248.2312</v>
       </c>
       <c r="G77">
         <v>65.09999999999999</v>
@@ -7857,45 +7857,45 @@
         <v>33.296</v>
       </c>
       <c r="M77">
-        <v>22.04685</v>
+        <v>36.44034016000001</v>
       </c>
       <c r="N77">
-        <v>11.24915</v>
+        <v>-3.144340160000006</v>
       </c>
       <c r="O77">
-        <v>1.6873725</v>
+        <v>-0.4716510240000009</v>
       </c>
       <c r="P77">
-        <v>9.5617775</v>
+        <v>-2.672689136000005</v>
       </c>
       <c r="Q77">
-        <v>10.1657775</v>
+        <v>-2.068689136000005</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2406831905091387</v>
+        <v>0.2507102411002707</v>
       </c>
       <c r="T77">
-        <v>2.539981279538538</v>
+        <v>2.670667362437344</v>
       </c>
       <c r="U77">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.15</v>
+        <v>0.13705689842825</v>
       </c>
       <c r="W77">
-        <v>0.0765</v>
+        <v>0.1266800473107329</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.510238424083259</v>
+        <v>0.9137126561883333</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7903,22 +7903,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.156447293820222</v>
+        <v>0.157457293820222</v>
       </c>
       <c r="C78">
-        <v>-21.49038801449083</v>
+        <v>-25.86875720336516</v>
       </c>
       <c r="D78">
-        <v>161.6408119855092</v>
+        <v>160.5286427966348</v>
       </c>
       <c r="E78">
-        <v>246.5112</v>
+        <v>249.7774</v>
       </c>
       <c r="F78">
-        <v>248.2312</v>
+        <v>251.4974</v>
       </c>
       <c r="G78">
         <v>65.09999999999999</v>
@@ -7939,37 +7939,37 @@
         <v>33.296</v>
       </c>
       <c r="M78">
-        <v>36.44034016000001</v>
+        <v>36.91981832</v>
       </c>
       <c r="N78">
-        <v>-3.144340160000006</v>
+        <v>-3.623818320000005</v>
       </c>
       <c r="O78">
-        <v>-0.4716510240000009</v>
+        <v>-0.5435727480000008</v>
       </c>
       <c r="P78">
-        <v>-2.672689136000005</v>
+        <v>-3.080245572000004</v>
       </c>
       <c r="Q78">
-        <v>-2.068689136000005</v>
+        <v>-2.476245572000004</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2507102411002707</v>
+        <v>0.2596193820176738</v>
       </c>
       <c r="T78">
-        <v>2.670667362437344</v>
+        <v>2.786783334717228</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.13705689842825</v>
+        <v>0.1352769387084026</v>
       </c>
       <c r="W78">
-        <v>0.1266800473107329</v>
+        <v>0.1269413453976065</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9137126561883333</v>
+        <v>0.9018462580560173</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7985,22 +7985,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.157457293820222</v>
+        <v>0.158467293820222</v>
       </c>
       <c r="C79">
-        <v>-25.86875720336516</v>
+        <v>-30.23192642114526</v>
       </c>
       <c r="D79">
-        <v>160.5286427966348</v>
+        <v>159.4316735788548</v>
       </c>
       <c r="E79">
-        <v>249.7774</v>
+        <v>253.0436</v>
       </c>
       <c r="F79">
-        <v>251.4974</v>
+        <v>254.7636</v>
       </c>
       <c r="G79">
         <v>65.09999999999999</v>
@@ -8021,37 +8021,37 @@
         <v>33.296</v>
       </c>
       <c r="M79">
-        <v>36.91981832</v>
+        <v>37.39929648</v>
       </c>
       <c r="N79">
-        <v>-3.623818320000005</v>
+        <v>-4.103296480000004</v>
       </c>
       <c r="O79">
-        <v>-0.5435727480000008</v>
+        <v>-0.6154944720000006</v>
       </c>
       <c r="P79">
-        <v>-3.080245572000004</v>
+        <v>-3.487802008000004</v>
       </c>
       <c r="Q79">
-        <v>-2.476245572000004</v>
+        <v>-2.883802008000004</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2596193820176738</v>
+        <v>0.2693384448366589</v>
       </c>
       <c r="T79">
-        <v>2.786783334717228</v>
+        <v>2.913455304477102</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1352769387084026</v>
+        <v>0.1335426189813718</v>
       </c>
       <c r="W79">
-        <v>0.1269413453976065</v>
+        <v>0.1271959435335346</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9018462580560173</v>
+        <v>0.8902841265424787</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8067,22 +8067,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.158467293820222</v>
+        <v>0.159477293820222</v>
       </c>
       <c r="C80">
-        <v>-30.23192642114526</v>
+        <v>-34.58020515900984</v>
       </c>
       <c r="D80">
-        <v>159.4316735788548</v>
+        <v>158.3495948409902</v>
       </c>
       <c r="E80">
-        <v>253.0436</v>
+        <v>256.3098</v>
       </c>
       <c r="F80">
-        <v>254.7636</v>
+        <v>258.0298</v>
       </c>
       <c r="G80">
         <v>65.09999999999999</v>
@@ -8103,37 +8103,37 @@
         <v>33.296</v>
       </c>
       <c r="M80">
-        <v>37.39929648</v>
+        <v>37.87877464000001</v>
       </c>
       <c r="N80">
-        <v>-4.103296480000004</v>
+        <v>-4.582774640000011</v>
       </c>
       <c r="O80">
-        <v>-0.6154944720000006</v>
+        <v>-0.6874161960000016</v>
       </c>
       <c r="P80">
-        <v>-3.487802008000004</v>
+        <v>-3.895358444000009</v>
       </c>
       <c r="Q80">
-        <v>-2.883802008000004</v>
+        <v>-3.291358444000009</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2693384448366589</v>
+        <v>0.2799831326860236</v>
       </c>
       <c r="T80">
-        <v>2.913455304477102</v>
+        <v>3.052191271356964</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1335426189813718</v>
+        <v>0.1318522060828734</v>
       </c>
       <c r="W80">
-        <v>0.1271959435335346</v>
+        <v>0.1274440961470342</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8902841265424787</v>
+        <v>0.879014707219156</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8149,22 +8149,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.159477293820222</v>
+        <v>0.160487293820222</v>
       </c>
       <c r="C81">
-        <v>-34.58020515900984</v>
+        <v>-38.91389456258955</v>
       </c>
       <c r="D81">
-        <v>158.3495948409902</v>
+        <v>157.2821054374105</v>
       </c>
       <c r="E81">
-        <v>256.3098</v>
+        <v>259.576</v>
       </c>
       <c r="F81">
-        <v>258.0298</v>
+        <v>261.296</v>
       </c>
       <c r="G81">
         <v>65.09999999999999</v>
@@ -8185,37 +8185,37 @@
         <v>33.296</v>
       </c>
       <c r="M81">
-        <v>37.87877464000001</v>
+        <v>38.3582528</v>
       </c>
       <c r="N81">
-        <v>-4.582774640000011</v>
+        <v>-5.062252800000003</v>
       </c>
       <c r="O81">
-        <v>-0.6874161960000016</v>
+        <v>-0.7593379200000004</v>
       </c>
       <c r="P81">
-        <v>-3.895358444000009</v>
+        <v>-4.302914880000003</v>
       </c>
       <c r="Q81">
-        <v>-3.291358444000009</v>
+        <v>-3.698914880000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2799831326860236</v>
+        <v>0.2916922893203249</v>
       </c>
       <c r="T81">
-        <v>3.052191271356964</v>
+        <v>3.204800834924813</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1318522060828734</v>
+        <v>0.1302040535068375</v>
       </c>
       <c r="W81">
-        <v>0.1274440961470342</v>
+        <v>0.1276860449451963</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.879014707219156</v>
+        <v>0.8680270233789167</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8231,22 +8231,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.160487293820222</v>
+        <v>0.161497293820222</v>
       </c>
       <c r="C82">
-        <v>-38.91389456258955</v>
+        <v>-43.23328771138387</v>
       </c>
       <c r="D82">
-        <v>157.2821054374105</v>
+        <v>156.2289122886162</v>
       </c>
       <c r="E82">
-        <v>259.576</v>
+        <v>262.8422</v>
       </c>
       <c r="F82">
-        <v>261.296</v>
+        <v>264.5622</v>
       </c>
       <c r="G82">
         <v>65.09999999999999</v>
@@ -8267,37 +8267,37 @@
         <v>33.296</v>
       </c>
       <c r="M82">
-        <v>38.3582528</v>
+        <v>38.83773096000001</v>
       </c>
       <c r="N82">
-        <v>-5.062252800000003</v>
+        <v>-5.54173096000001</v>
       </c>
       <c r="O82">
-        <v>-0.7593379200000004</v>
+        <v>-0.8312596440000014</v>
       </c>
       <c r="P82">
-        <v>-4.302914880000003</v>
+        <v>-4.710471316000008</v>
       </c>
       <c r="Q82">
-        <v>-3.698914880000003</v>
+        <v>-4.106471316000008</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2916922893203249</v>
+        <v>0.3046339887582367</v>
       </c>
       <c r="T82">
-        <v>3.204800834924813</v>
+        <v>3.373474563078751</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1302040535068375</v>
+        <v>0.1285965960561358</v>
       </c>
       <c r="W82">
-        <v>0.1276860449451963</v>
+        <v>0.1279220196989593</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8680270233789167</v>
+        <v>0.8573106403742385</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8313,22 +8313,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.161497293820222</v>
+        <v>0.162507293820222</v>
       </c>
       <c r="C83">
-        <v>-43.23328771138387</v>
+        <v>-47.53866988702725</v>
       </c>
       <c r="D83">
-        <v>156.2289122886162</v>
+        <v>155.1897301129728</v>
       </c>
       <c r="E83">
-        <v>262.8422</v>
+        <v>266.1084</v>
       </c>
       <c r="F83">
-        <v>264.5622</v>
+        <v>267.8284</v>
       </c>
       <c r="G83">
         <v>65.09999999999999</v>
@@ -8349,37 +8349,37 @@
         <v>33.296</v>
       </c>
       <c r="M83">
-        <v>38.83773096000001</v>
+        <v>39.31720912000001</v>
       </c>
       <c r="N83">
-        <v>-5.54173096000001</v>
+        <v>-6.021209120000009</v>
       </c>
       <c r="O83">
-        <v>-0.8312596440000014</v>
+        <v>-0.9031813680000013</v>
       </c>
       <c r="P83">
-        <v>-4.710471316000008</v>
+        <v>-5.118027752000008</v>
       </c>
       <c r="Q83">
-        <v>-4.106471316000008</v>
+        <v>-4.514027752000008</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3046339887582367</v>
+        <v>0.319013654800361</v>
       </c>
       <c r="T83">
-        <v>3.373474563078751</v>
+        <v>3.560889816583126</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1285965960561358</v>
+        <v>0.1270283448847195</v>
       </c>
       <c r="W83">
-        <v>0.1279220196989593</v>
+        <v>0.1281522389709232</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8573106403742385</v>
+        <v>0.8468556325647967</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8395,22 +8395,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.162507293820222</v>
+        <v>0.163517293820222</v>
       </c>
       <c r="C84">
-        <v>-47.53866988702725</v>
+        <v>-51.8303188309194</v>
       </c>
       <c r="D84">
-        <v>155.1897301129728</v>
+        <v>154.1642811690806</v>
       </c>
       <c r="E84">
-        <v>266.1084</v>
+        <v>269.3746</v>
       </c>
       <c r="F84">
-        <v>267.8284</v>
+        <v>271.0946</v>
       </c>
       <c r="G84">
         <v>65.09999999999999</v>
@@ -8431,37 +8431,37 @@
         <v>33.296</v>
       </c>
       <c r="M84">
-        <v>39.31720912000001</v>
+        <v>39.79668728000001</v>
       </c>
       <c r="N84">
-        <v>-6.021209120000009</v>
+        <v>-6.500687280000008</v>
       </c>
       <c r="O84">
-        <v>-0.9031813680000013</v>
+        <v>-0.9751030920000012</v>
       </c>
       <c r="P84">
-        <v>-5.118027752000008</v>
+        <v>-5.525584188000007</v>
       </c>
       <c r="Q84">
-        <v>-4.514027752000008</v>
+        <v>-4.921584188000007</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.319013654800361</v>
+        <v>0.3350850462592058</v>
       </c>
       <c r="T84">
-        <v>3.560889816583126</v>
+        <v>3.770353923440957</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1270283448847195</v>
+        <v>0.1254978828981566</v>
       </c>
       <c r="W84">
-        <v>0.1281522389709232</v>
+        <v>0.1283769107905506</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8468556325647967</v>
+        <v>0.8366525526543774</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8477,22 +8477,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.163517293820222</v>
+        <v>0.164527293820222</v>
       </c>
       <c r="C85">
-        <v>-51.8303188309194</v>
+        <v>-56.10850499170843</v>
       </c>
       <c r="D85">
-        <v>154.1642811690806</v>
+        <v>153.1522950082916</v>
       </c>
       <c r="E85">
-        <v>269.3746</v>
+        <v>272.6408</v>
       </c>
       <c r="F85">
-        <v>271.0946</v>
+        <v>274.3608</v>
       </c>
       <c r="G85">
         <v>65.09999999999999</v>
@@ -8513,37 +8513,37 @@
         <v>33.296</v>
       </c>
       <c r="M85">
-        <v>39.79668728000001</v>
+        <v>40.27616544000001</v>
       </c>
       <c r="N85">
-        <v>-6.500687280000008</v>
+        <v>-6.980165440000007</v>
       </c>
       <c r="O85">
-        <v>-0.9751030920000012</v>
+        <v>-1.047024816000001</v>
       </c>
       <c r="P85">
-        <v>-5.525584188000007</v>
+        <v>-5.933140624000006</v>
       </c>
       <c r="Q85">
-        <v>-4.921584188000007</v>
+        <v>-5.329140624000006</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3350850462592058</v>
+        <v>0.3531653616504062</v>
       </c>
       <c r="T85">
-        <v>3.770353923440957</v>
+        <v>4.006001043656018</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1254978828981566</v>
+        <v>0.1240038604827024</v>
       </c>
       <c r="W85">
-        <v>0.1283769107905506</v>
+        <v>0.1285962332811393</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8366525526543774</v>
+        <v>0.8266924032180158</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8559,22 +8559,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.164527293820222</v>
+        <v>0.1655372938202219</v>
       </c>
       <c r="C86">
-        <v>-56.10850499170832</v>
+        <v>-60.37349176309007</v>
       </c>
       <c r="D86">
-        <v>153.1522950082917</v>
+        <v>152.1535082369099</v>
       </c>
       <c r="E86">
-        <v>272.6408</v>
+        <v>275.907</v>
       </c>
       <c r="F86">
-        <v>274.3608</v>
+        <v>277.627</v>
       </c>
       <c r="G86">
         <v>65.09999999999999</v>
@@ -8595,37 +8595,37 @@
         <v>33.296</v>
       </c>
       <c r="M86">
-        <v>40.27616544</v>
+        <v>40.75564360000001</v>
       </c>
       <c r="N86">
-        <v>-6.98016544</v>
+        <v>-7.459643600000007</v>
       </c>
       <c r="O86">
-        <v>-1.047024816</v>
+        <v>-1.118946540000001</v>
       </c>
       <c r="P86">
-        <v>-5.933140624</v>
+        <v>-6.340697060000005</v>
       </c>
       <c r="Q86">
-        <v>-5.329140624</v>
+        <v>-5.736697060000005</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3531653616504059</v>
+        <v>0.373656385760433</v>
       </c>
       <c r="T86">
-        <v>4.006001043656014</v>
+        <v>4.273067779899749</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1240038604827024</v>
+        <v>0.122544991535847</v>
       </c>
       <c r="W86">
-        <v>0.1285962332811393</v>
+        <v>0.1288103952425377</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.826692403218016</v>
+        <v>0.8169666102389803</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8641,22 +8641,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1655372938202219</v>
+        <v>0.166547293820222</v>
       </c>
       <c r="C87">
-        <v>-60.37349176309007</v>
+        <v>-64.62553571236285</v>
       </c>
       <c r="D87">
-        <v>152.1535082369099</v>
+        <v>151.1676642876371</v>
       </c>
       <c r="E87">
-        <v>275.907</v>
+        <v>279.1732</v>
       </c>
       <c r="F87">
-        <v>277.627</v>
+        <v>280.8932</v>
       </c>
       <c r="G87">
         <v>65.09999999999999</v>
@@ -8677,37 +8677,37 @@
         <v>33.296</v>
       </c>
       <c r="M87">
-        <v>40.75564360000001</v>
+        <v>41.23512176</v>
       </c>
       <c r="N87">
-        <v>-7.459643600000007</v>
+        <v>-7.939121759999999</v>
       </c>
       <c r="O87">
-        <v>-1.118946540000001</v>
+        <v>-1.190868264</v>
       </c>
       <c r="P87">
-        <v>-6.340697060000005</v>
+        <v>-6.748253495999999</v>
       </c>
       <c r="Q87">
-        <v>-5.736697060000005</v>
+        <v>-6.144253495999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.373656385760433</v>
+        <v>0.3970746990290354</v>
       </c>
       <c r="T87">
-        <v>4.273067779899749</v>
+        <v>4.578286907035446</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.122544991535847</v>
+        <v>0.1211200497738023</v>
       </c>
       <c r="W87">
-        <v>0.1288103952425377</v>
+        <v>0.1290195766932058</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8169666102389803</v>
+        <v>0.8074669984920156</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8723,22 +8723,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.166547293820222</v>
+        <v>0.2160750609418092</v>
       </c>
       <c r="C88">
-        <v>-64.62553571236285</v>
+        <v>-104.3408658973169</v>
       </c>
       <c r="D88">
-        <v>151.1676642876371</v>
+        <v>114.7185341026831</v>
       </c>
       <c r="E88">
-        <v>279.1732</v>
+        <v>282.4394</v>
       </c>
       <c r="F88">
-        <v>280.8932</v>
+        <v>284.1594</v>
       </c>
       <c r="G88">
         <v>65.09999999999999</v>
@@ -8759,45 +8759,45 @@
         <v>33.296</v>
       </c>
       <c r="M88">
-        <v>41.23512176</v>
+        <v>57.05920752</v>
       </c>
       <c r="N88">
-        <v>-7.939121759999999</v>
+        <v>-23.76320752</v>
       </c>
       <c r="O88">
-        <v>-1.190868264</v>
+        <v>-3.564481128</v>
       </c>
       <c r="P88">
-        <v>-6.748253495999999</v>
+        <v>-20.198726392</v>
       </c>
       <c r="Q88">
-        <v>-6.144253495999999</v>
+        <v>-19.594726392</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3970746990290354</v>
+        <v>0.4359248075819398</v>
       </c>
       <c r="T88">
-        <v>4.578286907035446</v>
+        <v>5.084634058755491</v>
       </c>
       <c r="U88">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1211200497738023</v>
+        <v>0.08753013259515385</v>
       </c>
       <c r="W88">
-        <v>0.1290195766932058</v>
+        <v>0.1832239493748931</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.8074669984920156</v>
+        <v>0.5835342173010256</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8805,22 +8805,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2160750609418092</v>
+        <v>0.2176250609418092</v>
       </c>
       <c r="C89">
-        <v>-104.3408658973169</v>
+        <v>-108.4662375958899</v>
       </c>
       <c r="D89">
-        <v>114.7185341026831</v>
+        <v>113.8593624041101</v>
       </c>
       <c r="E89">
-        <v>282.4394</v>
+        <v>285.7056</v>
       </c>
       <c r="F89">
-        <v>284.1594</v>
+        <v>287.4256</v>
       </c>
       <c r="G89">
         <v>65.09999999999999</v>
@@ -8841,37 +8841,37 @@
         <v>33.296</v>
       </c>
       <c r="M89">
-        <v>57.05920752</v>
+        <v>57.71506048000001</v>
       </c>
       <c r="N89">
-        <v>-23.76320752</v>
+        <v>-24.41906048000001</v>
       </c>
       <c r="O89">
-        <v>-3.564481128</v>
+        <v>-3.662859072000001</v>
       </c>
       <c r="P89">
-        <v>-20.198726392</v>
+        <v>-20.75620140800001</v>
       </c>
       <c r="Q89">
-        <v>-19.594726392</v>
+        <v>-20.15220140800001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4359248075819398</v>
+        <v>0.4684352082137682</v>
       </c>
       <c r="T89">
-        <v>5.084634058755491</v>
+        <v>5.508353563651783</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08753013259515385</v>
+        <v>0.08653547199748164</v>
       </c>
       <c r="W89">
-        <v>0.1832239493748931</v>
+        <v>0.1834236772229057</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5835342173010256</v>
+        <v>0.5769031466498776</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8887,22 +8887,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2176250609418092</v>
+        <v>0.2191750609418092</v>
       </c>
       <c r="C90">
-        <v>-108.4662375958899</v>
+        <v>-112.5788356197734</v>
       </c>
       <c r="D90">
-        <v>113.8593624041101</v>
+        <v>113.0129643802266</v>
       </c>
       <c r="E90">
-        <v>285.7056</v>
+        <v>288.9718</v>
       </c>
       <c r="F90">
-        <v>287.4256</v>
+        <v>290.6918</v>
       </c>
       <c r="G90">
         <v>65.09999999999999</v>
@@ -8923,37 +8923,37 @@
         <v>33.296</v>
       </c>
       <c r="M90">
-        <v>57.71506048000001</v>
+        <v>58.37091344</v>
       </c>
       <c r="N90">
-        <v>-24.41906048000001</v>
+        <v>-25.07491344</v>
       </c>
       <c r="O90">
-        <v>-3.662859072000001</v>
+        <v>-3.761237016</v>
       </c>
       <c r="P90">
-        <v>-20.75620140800001</v>
+        <v>-21.313676424</v>
       </c>
       <c r="Q90">
-        <v>-20.15220140800001</v>
+        <v>-20.709676424</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4684352082137682</v>
+        <v>0.5068565907786562</v>
       </c>
       <c r="T90">
-        <v>5.508353563651783</v>
+        <v>6.009112978529217</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08653547199748164</v>
+        <v>0.08556316332335265</v>
       </c>
       <c r="W90">
-        <v>0.1834236772229057</v>
+        <v>0.1836189168046708</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5769031466498776</v>
+        <v>0.5704210888223509</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8969,22 +8969,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2191750609418092</v>
+        <v>0.2207250609418092</v>
       </c>
       <c r="C91">
-        <v>-112.5788356197734</v>
+        <v>-116.6789427345316</v>
       </c>
       <c r="D91">
-        <v>113.0129643802266</v>
+        <v>112.1790572654684</v>
       </c>
       <c r="E91">
-        <v>288.9718</v>
+        <v>292.238</v>
       </c>
       <c r="F91">
-        <v>290.6918</v>
+        <v>293.958</v>
       </c>
       <c r="G91">
         <v>65.09999999999999</v>
@@ -9005,37 +9005,37 @@
         <v>33.296</v>
       </c>
       <c r="M91">
-        <v>58.37091344</v>
+        <v>59.02676640000001</v>
       </c>
       <c r="N91">
-        <v>-25.07491344</v>
+        <v>-25.73076640000001</v>
       </c>
       <c r="O91">
-        <v>-3.761237016</v>
+        <v>-3.859614960000001</v>
       </c>
       <c r="P91">
-        <v>-21.313676424</v>
+        <v>-21.87115144000001</v>
       </c>
       <c r="Q91">
-        <v>-20.709676424</v>
+        <v>-21.26715144000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5068565907786562</v>
+        <v>0.5529622498565219</v>
       </c>
       <c r="T91">
-        <v>6.009112978529217</v>
+        <v>6.61002427638214</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.08556316332335265</v>
+        <v>0.08461246150864872</v>
       </c>
       <c r="W91">
-        <v>0.1836189168046708</v>
+        <v>0.1838098177290633</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5704210888223509</v>
+        <v>0.5640830767243248</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9051,22 +9051,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2207250609418092</v>
+        <v>0.2222750609418092</v>
       </c>
       <c r="C92">
-        <v>-116.6789427345316</v>
+        <v>-120.7668334209081</v>
       </c>
       <c r="D92">
-        <v>112.1790572654684</v>
+        <v>111.3573665790919</v>
       </c>
       <c r="E92">
-        <v>292.238</v>
+        <v>295.5042</v>
       </c>
       <c r="F92">
-        <v>293.958</v>
+        <v>297.2242</v>
       </c>
       <c r="G92">
         <v>65.09999999999999</v>
@@ -9087,37 +9087,37 @@
         <v>33.296</v>
       </c>
       <c r="M92">
-        <v>59.02676640000001</v>
+        <v>59.68261936</v>
       </c>
       <c r="N92">
-        <v>-25.73076640000001</v>
+        <v>-26.38661936</v>
       </c>
       <c r="O92">
-        <v>-3.859614960000001</v>
+        <v>-3.957992904000001</v>
       </c>
       <c r="P92">
-        <v>-21.87115144000001</v>
+        <v>-22.428626456</v>
       </c>
       <c r="Q92">
-        <v>-21.26715144000001</v>
+        <v>-21.824626456</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5529622498565219</v>
+        <v>0.609313610951691</v>
       </c>
       <c r="T92">
-        <v>6.61002427638214</v>
+        <v>7.344471418202379</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08461246150864872</v>
+        <v>0.0836826542393229</v>
       </c>
       <c r="W92">
-        <v>0.1838098177290633</v>
+        <v>0.183996523028744</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5640830767243248</v>
+        <v>0.557884361595486</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9133,22 +9133,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2222750609418092</v>
+        <v>0.2238250609418092</v>
       </c>
       <c r="C93">
-        <v>-120.7668334209081</v>
+        <v>-124.8427741760441</v>
       </c>
       <c r="D93">
-        <v>111.3573665790919</v>
+        <v>110.5476258239559</v>
       </c>
       <c r="E93">
-        <v>295.5042</v>
+        <v>298.7704</v>
       </c>
       <c r="F93">
-        <v>297.2242</v>
+        <v>300.4904</v>
       </c>
       <c r="G93">
         <v>65.09999999999999</v>
@@ -9169,37 +9169,37 @@
         <v>33.296</v>
       </c>
       <c r="M93">
-        <v>59.68261936</v>
+        <v>60.33847232000001</v>
       </c>
       <c r="N93">
-        <v>-26.38661936</v>
+        <v>-27.04247232000001</v>
       </c>
       <c r="O93">
-        <v>-3.957992904000001</v>
+        <v>-4.056370848000001</v>
       </c>
       <c r="P93">
-        <v>-22.428626456</v>
+        <v>-22.98610147200001</v>
       </c>
       <c r="Q93">
-        <v>-21.824626456</v>
+        <v>-22.38210147200001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.609313610951691</v>
+        <v>0.6797528123206527</v>
       </c>
       <c r="T93">
-        <v>7.344471418202379</v>
+        <v>8.262530345477678</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.0836826542393229</v>
+        <v>0.08277306017150417</v>
       </c>
       <c r="W93">
-        <v>0.183996523028744</v>
+        <v>0.184179169517562</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.557884361595486</v>
+        <v>0.5518204011433612</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9215,22 +9215,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2238250609418092</v>
+        <v>0.2253750609418092</v>
       </c>
       <c r="C94">
-        <v>-124.8427741760441</v>
+        <v>-128.9070238016483</v>
       </c>
       <c r="D94">
-        <v>110.5476258239559</v>
+        <v>109.7495761983518</v>
       </c>
       <c r="E94">
-        <v>298.7704</v>
+        <v>302.0366</v>
       </c>
       <c r="F94">
-        <v>300.4904</v>
+        <v>303.7566</v>
       </c>
       <c r="G94">
         <v>65.09999999999999</v>
@@ -9251,37 +9251,37 @@
         <v>33.296</v>
       </c>
       <c r="M94">
-        <v>60.33847232000001</v>
+        <v>60.99432528000001</v>
       </c>
       <c r="N94">
-        <v>-27.04247232000001</v>
+        <v>-27.69832528000001</v>
       </c>
       <c r="O94">
-        <v>-4.056370848000001</v>
+        <v>-4.154748792000002</v>
       </c>
       <c r="P94">
-        <v>-22.98610147200001</v>
+        <v>-23.54357648800001</v>
       </c>
       <c r="Q94">
-        <v>-22.38210147200001</v>
+        <v>-22.93957648800001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6797528123206527</v>
+        <v>0.7703174997950317</v>
       </c>
       <c r="T94">
-        <v>8.262530345477678</v>
+        <v>9.442891823403063</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08277306017150417</v>
+        <v>0.08188302726643423</v>
       </c>
       <c r="W94">
-        <v>0.184179169517562</v>
+        <v>0.1843578881249</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5518204011433612</v>
+        <v>0.5458868484428949</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9297,22 +9297,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2253750609418092</v>
+        <v>0.2269250609418092</v>
       </c>
       <c r="C95">
-        <v>-128.9070238016483</v>
+        <v>-132.9598336797749</v>
       </c>
       <c r="D95">
-        <v>109.7495761983518</v>
+        <v>108.9629663202251</v>
       </c>
       <c r="E95">
-        <v>302.0366</v>
+        <v>305.3028</v>
       </c>
       <c r="F95">
-        <v>303.7566</v>
+        <v>307.0228</v>
       </c>
       <c r="G95">
         <v>65.09999999999999</v>
@@ -9333,37 +9333,37 @@
         <v>33.296</v>
       </c>
       <c r="M95">
-        <v>60.99432528000001</v>
+        <v>61.65017824</v>
       </c>
       <c r="N95">
-        <v>-27.69832528000001</v>
+        <v>-28.35417824</v>
       </c>
       <c r="O95">
-        <v>-4.154748792000002</v>
+        <v>-4.253126736</v>
       </c>
       <c r="P95">
-        <v>-23.54357648800001</v>
+        <v>-24.101051504</v>
       </c>
       <c r="Q95">
-        <v>-22.93957648800001</v>
+        <v>-23.49705150400001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7703174997950317</v>
+        <v>0.891070416427537</v>
       </c>
       <c r="T95">
-        <v>9.442891823403063</v>
+        <v>11.01670712730357</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08188302726643423</v>
+        <v>0.08101193123168494</v>
       </c>
       <c r="W95">
-        <v>0.1843578881249</v>
+        <v>0.1845328042086777</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5458868484428949</v>
+        <v>0.5400795415445663</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9379,22 +9379,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2269250609418092</v>
+        <v>0.2284750609418092</v>
       </c>
       <c r="C96">
-        <v>-132.9598336797749</v>
+        <v>-137.0014480368269</v>
       </c>
       <c r="D96">
-        <v>108.9629663202251</v>
+        <v>108.1875519631731</v>
       </c>
       <c r="E96">
-        <v>305.3028</v>
+        <v>308.569</v>
       </c>
       <c r="F96">
-        <v>307.0228</v>
+        <v>310.289</v>
       </c>
       <c r="G96">
         <v>65.09999999999999</v>
@@ -9415,37 +9415,37 @@
         <v>33.296</v>
       </c>
       <c r="M96">
-        <v>61.65017824</v>
+        <v>62.30603120000001</v>
       </c>
       <c r="N96">
-        <v>-28.35417824</v>
+        <v>-29.01003120000001</v>
       </c>
       <c r="O96">
-        <v>-4.253126736</v>
+        <v>-4.351504680000002</v>
       </c>
       <c r="P96">
-        <v>-24.101051504</v>
+        <v>-24.65852652000001</v>
       </c>
       <c r="Q96">
-        <v>-23.49705150400001</v>
+        <v>-24.05452652000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.891070416427537</v>
+        <v>1.060124499713045</v>
       </c>
       <c r="T96">
-        <v>11.01670712730357</v>
+        <v>13.2200485527643</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.08101193123168494</v>
+        <v>0.08015917406082509</v>
       </c>
       <c r="W96">
-        <v>0.1845328042086777</v>
+        <v>0.1847040378485863</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5400795415445663</v>
+        <v>0.534394493738834</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9461,22 +9461,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2284750609418092</v>
+        <v>0.2300250609418092</v>
       </c>
       <c r="C97">
-        <v>-137.0014480368269</v>
+        <v>-141.0321041963656</v>
       </c>
       <c r="D97">
-        <v>108.1875519631731</v>
+        <v>107.4230958036345</v>
       </c>
       <c r="E97">
-        <v>308.569</v>
+        <v>311.8352</v>
       </c>
       <c r="F97">
-        <v>310.289</v>
+        <v>313.5552</v>
       </c>
       <c r="G97">
         <v>65.09999999999999</v>
@@ -9497,37 +9497,37 @@
         <v>33.296</v>
       </c>
       <c r="M97">
-        <v>62.30603120000001</v>
+        <v>62.96188416</v>
       </c>
       <c r="N97">
-        <v>-29.01003120000001</v>
+        <v>-29.66588416</v>
       </c>
       <c r="O97">
-        <v>-4.351504680000002</v>
+        <v>-4.449882624000001</v>
       </c>
       <c r="P97">
-        <v>-24.65852652000001</v>
+        <v>-25.216001536</v>
       </c>
       <c r="Q97">
-        <v>-24.05452652000001</v>
+        <v>-24.612001536</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.060124499713045</v>
+        <v>1.313705624641307</v>
       </c>
       <c r="T97">
-        <v>13.2200485527643</v>
+        <v>16.52506069095538</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.08015917406082509</v>
+        <v>0.07932418266435817</v>
       </c>
       <c r="W97">
-        <v>0.1847040378485863</v>
+        <v>0.1848717041209969</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.534394493738834</v>
+        <v>0.5288278844290545</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9543,22 +9543,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2300250609418092</v>
+        <v>0.2315750609418092</v>
       </c>
       <c r="C98">
-        <v>-141.0321041963656</v>
+        <v>-145.0520328212783</v>
       </c>
       <c r="D98">
-        <v>107.4230958036345</v>
+        <v>106.6693671787217</v>
       </c>
       <c r="E98">
-        <v>311.8352</v>
+        <v>315.1014</v>
       </c>
       <c r="F98">
-        <v>313.5552</v>
+        <v>316.8214</v>
       </c>
       <c r="G98">
         <v>65.09999999999999</v>
@@ -9579,37 +9579,37 @@
         <v>33.296</v>
       </c>
       <c r="M98">
-        <v>62.96188416</v>
+        <v>63.61773712</v>
       </c>
       <c r="N98">
-        <v>-29.66588416</v>
+        <v>-30.32173712</v>
       </c>
       <c r="O98">
-        <v>-4.449882624000001</v>
+        <v>-4.548260568</v>
       </c>
       <c r="P98">
-        <v>-25.216001536</v>
+        <v>-25.773476552</v>
       </c>
       <c r="Q98">
-        <v>-24.612001536</v>
+        <v>-25.169476552</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.313705624641304</v>
+        <v>1.736340832855071</v>
       </c>
       <c r="T98">
-        <v>16.52506069095534</v>
+        <v>22.03341425460711</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.07932418266435817</v>
+        <v>0.07850640758534418</v>
       </c>
       <c r="W98">
-        <v>0.1848717041209969</v>
+        <v>0.1850359133568629</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5288278844290545</v>
+        <v>0.5233760505689612</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9625,22 +9625,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2315750609418092</v>
+        <v>0.2331250609418092</v>
       </c>
       <c r="C99">
-        <v>-145.0520328212783</v>
+        <v>-149.0614581458212</v>
       </c>
       <c r="D99">
-        <v>106.6693671787217</v>
+        <v>105.9261418541789</v>
       </c>
       <c r="E99">
-        <v>315.1014</v>
+        <v>318.3676</v>
       </c>
       <c r="F99">
-        <v>316.8214</v>
+        <v>320.0876</v>
       </c>
       <c r="G99">
         <v>65.09999999999999</v>
@@ -9661,37 +9661,37 @@
         <v>33.296</v>
       </c>
       <c r="M99">
-        <v>63.61773712</v>
+        <v>64.27359008000001</v>
       </c>
       <c r="N99">
-        <v>-30.32173712</v>
+        <v>-30.97759008000001</v>
       </c>
       <c r="O99">
-        <v>-4.548260568</v>
+        <v>-4.646638512000001</v>
       </c>
       <c r="P99">
-        <v>-25.773476552</v>
+        <v>-26.330951568</v>
       </c>
       <c r="Q99">
-        <v>-25.169476552</v>
+        <v>-25.726951568</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.736340832855071</v>
+        <v>2.581611249282607</v>
       </c>
       <c r="T99">
-        <v>22.03341425460711</v>
+        <v>33.05012138191067</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.07850640758534418</v>
+        <v>0.07770532179365698</v>
       </c>
       <c r="W99">
-        <v>0.1850359133568629</v>
+        <v>0.1851967713838337</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5233760505689612</v>
+        <v>0.5180354786243799</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9707,22 +9707,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2331250609418092</v>
+        <v>0.2346750609418092</v>
       </c>
       <c r="C100">
-        <v>-149.0614581458212</v>
+        <v>-153.0605981980291</v>
       </c>
       <c r="D100">
-        <v>105.9261418541789</v>
+        <v>105.1932018019708</v>
       </c>
       <c r="E100">
-        <v>318.3676</v>
+        <v>321.6338</v>
       </c>
       <c r="F100">
-        <v>320.0876</v>
+        <v>323.3538</v>
       </c>
       <c r="G100">
         <v>65.09999999999999</v>
@@ -9743,37 +9743,37 @@
         <v>33.296</v>
       </c>
       <c r="M100">
-        <v>64.27359008000001</v>
+        <v>64.92944304</v>
       </c>
       <c r="N100">
-        <v>-30.97759008000001</v>
+        <v>-31.63344304</v>
       </c>
       <c r="O100">
-        <v>-4.646638512000001</v>
+        <v>-4.745016455999999</v>
       </c>
       <c r="P100">
-        <v>-26.330951568</v>
+        <v>-26.888426584</v>
       </c>
       <c r="Q100">
-        <v>-25.726951568</v>
+        <v>-26.284426584</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.581611249282607</v>
+        <v>5.117422498565213</v>
       </c>
       <c r="T100">
-        <v>33.05012138191067</v>
+        <v>66.10024276382133</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.07770532179365698</v>
+        <v>0.07692041955331702</v>
       </c>
       <c r="W100">
-        <v>0.1851967713838337</v>
+        <v>0.1853543797536939</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9781,91 +9781,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5180354786243799</v>
+        <v>0.5128027970221135</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2346750609418092</v>
-      </c>
-      <c r="C101">
-        <v>-153.0605981980291</v>
-      </c>
-      <c r="D101">
-        <v>105.1932018019708</v>
-      </c>
-      <c r="E101">
-        <v>321.6338</v>
-      </c>
-      <c r="F101">
-        <v>323.3538</v>
-      </c>
-      <c r="G101">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="H101">
-        <v>324.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>33.9</v>
-      </c>
-      <c r="K101">
-        <v>0.604</v>
-      </c>
-      <c r="L101">
-        <v>33.296</v>
-      </c>
-      <c r="M101">
-        <v>64.92944304</v>
-      </c>
-      <c r="N101">
-        <v>-31.63344304</v>
-      </c>
-      <c r="O101">
-        <v>-4.745016455999999</v>
-      </c>
-      <c r="P101">
-        <v>-26.888426584</v>
-      </c>
-      <c r="Q101">
-        <v>-26.284426584</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.117422498565213</v>
-      </c>
-      <c r="T101">
-        <v>66.10024276382133</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.07692041955331702</v>
-      </c>
-      <c r="W101">
-        <v>0.1853543797536939</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5128027970221135</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
